--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4745BC24-97AE-4A14-9758-0DBE1A3A6CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CDFBE7-8648-40E2-A2CE-578266086F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="2330" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3200" yWindow="2100" windowWidth="19380" windowHeight="10380" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="600">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -3504,9 +3504,6 @@
   </si>
   <si>
     <t>Annual Rate of Overseas Departures</t>
-  </si>
-  <si>
-    <t>rate</t>
   </si>
   <si>
     <t>Immigration Model</t>
@@ -5587,12 +5584,60 @@
   <si>
     <t>MTCT: HBeAg- undiagnosed</t>
   </si>
+  <si>
+    <t>mig_rate</t>
+  </si>
+  <si>
+    <t>Rate of migration (neg = emig)</t>
+  </si>
+  <si>
+    <t>max(total_pop*mig_rate, 0)</t>
+  </si>
+  <si>
+    <t>min(mig_rate,0)*-1</t>
+  </si>
+  <si>
+    <t>inc_hcc</t>
+  </si>
+  <si>
+    <t>Annual Incidence of HCC</t>
+  </si>
+  <si>
+    <t>:snk_hdth</t>
+  </si>
+  <si>
+    <t>(ei:hcc+eh:hcc+si:hcc+sh:hcc+cc:hcc+dc:hcc)+(ei_d:hcc_d+eh_d:hcc_d+si_d:hcc_d+sh_d:hcc_d+cc_d:hcc_d+dc_d:hcc_d)+(ei_l:hcc_l+eh_l:hcc_l+si_l:hcc_l+sh_l:hcc_l+cc_l:hcc_l+dc_l:hcc_l)+(ei_t:hcc_t+eh_t:hcc_t+si_t:hcc_t+sh_t:hcc_t+cc_t:hcc_t+dc_t:hcc_t)</t>
+  </si>
+  <si>
+    <t>chb_clr</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Natural History: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">HBsAg seroclearance </t>
+    </r>
+  </si>
+  <si>
+    <t>Total HBV attributable deaths</t>
+  </si>
+  <si>
+    <t>hep_dth</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5776,6 +5821,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -6070,7 +6122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6520,11 +6572,35 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -7003,79 +7079,79 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" t="s">
         <v>213</v>
-      </c>
-      <c r="B3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B5" t="s">
         <v>534</v>
-      </c>
-      <c r="B5" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B6" t="s">
         <v>536</v>
-      </c>
-      <c r="B6" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7" t="s">
         <v>538</v>
-      </c>
-      <c r="B7" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B8" t="s">
         <v>540</v>
-      </c>
-      <c r="B8" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>541</v>
+      </c>
+      <c r="B9" t="s">
         <v>542</v>
-      </c>
-      <c r="B9" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>545</v>
+      </c>
+      <c r="B10" t="s">
         <v>546</v>
-      </c>
-      <c r="B10" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>547</v>
+      </c>
+      <c r="B11" t="s">
         <v>548</v>
-      </c>
-      <c r="B11" t="s">
-        <v>549</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7568,12 +7644,12 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>AND(I2&lt;&gt;"",NOT(H2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9586,7 +9662,7 @@
       <c r="J8" s="31"/>
       <c r="K8" s="36"/>
       <c r="L8" s="36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M8" s="36"/>
       <c r="N8" s="36"/>
@@ -9832,14 +9908,16 @@
       <c r="H13" s="40"/>
       <c r="I13" s="40"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="40"/>
+      <c r="K13" s="40" t="s">
+        <v>596</v>
+      </c>
       <c r="L13" s="41"/>
       <c r="M13" s="42"/>
       <c r="N13" s="43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O13" s="44" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P13" s="45"/>
       <c r="Q13" s="46" t="s">
@@ -9889,7 +9967,9 @@
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
       <c r="J14" s="31"/>
-      <c r="K14" s="40"/>
+      <c r="K14" s="40" t="s">
+        <v>596</v>
+      </c>
       <c r="L14" s="41"/>
       <c r="M14" s="48"/>
       <c r="N14" s="40"/>
@@ -9944,7 +10024,9 @@
       <c r="H15" s="40"/>
       <c r="I15" s="40"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="40"/>
+      <c r="K15" s="40" t="s">
+        <v>596</v>
+      </c>
       <c r="L15" s="41"/>
       <c r="M15" s="48"/>
       <c r="N15" s="40" t="s">
@@ -10048,7 +10130,9 @@
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
-      <c r="K17" s="30"/>
+      <c r="K17" s="30" t="s">
+        <v>596</v>
+      </c>
       <c r="L17" s="30"/>
       <c r="M17" s="55"/>
       <c r="N17" s="55"/>
@@ -10056,10 +10140,10 @@
       <c r="P17" s="56"/>
       <c r="Q17" s="57"/>
       <c r="R17" s="43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S17" s="43" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T17" s="58"/>
       <c r="U17" s="59" t="s">
@@ -10107,7 +10191,9 @@
       <c r="H18" s="30"/>
       <c r="I18" s="30"/>
       <c r="J18" s="31"/>
-      <c r="K18" s="30"/>
+      <c r="K18" s="30" t="s">
+        <v>596</v>
+      </c>
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
       <c r="N18" s="30"/>
@@ -10164,7 +10250,9 @@
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
       <c r="J19" s="31"/>
-      <c r="K19" s="30"/>
+      <c r="K19" s="30" t="s">
+        <v>596</v>
+      </c>
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
@@ -10223,7 +10311,9 @@
       <c r="H20" s="30"/>
       <c r="I20" s="30"/>
       <c r="J20" s="31"/>
-      <c r="K20" s="30"/>
+      <c r="K20" s="30" t="s">
+        <v>596</v>
+      </c>
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
       <c r="N20" s="30"/>
@@ -10280,7 +10370,9 @@
       <c r="H21" s="34"/>
       <c r="I21" s="34"/>
       <c r="J21" s="31"/>
-      <c r="K21" s="34"/>
+      <c r="K21" s="34" t="s">
+        <v>596</v>
+      </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
@@ -10292,10 +10384,10 @@
       <c r="T21" s="70"/>
       <c r="U21" s="71"/>
       <c r="V21" s="43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="W21" s="72" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="X21" s="73"/>
       <c r="Y21" s="74" t="s">
@@ -10337,7 +10429,9 @@
       <c r="H22" s="34"/>
       <c r="I22" s="34"/>
       <c r="J22" s="31"/>
-      <c r="K22" s="34"/>
+      <c r="K22" s="34" t="s">
+        <v>596</v>
+      </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
       <c r="N22" s="34"/>
@@ -10392,7 +10486,9 @@
       <c r="H23" s="34"/>
       <c r="I23" s="34"/>
       <c r="J23" s="31"/>
-      <c r="K23" s="34"/>
+      <c r="K23" s="34" t="s">
+        <v>596</v>
+      </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
       <c r="N23" s="34"/>
@@ -10449,7 +10545,9 @@
       <c r="H24" s="34"/>
       <c r="I24" s="34"/>
       <c r="J24" s="31"/>
-      <c r="K24" s="34"/>
+      <c r="K24" s="34" t="s">
+        <v>596</v>
+      </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
       <c r="N24" s="34"/>
@@ -10502,7 +10600,9 @@
       <c r="H25" s="84"/>
       <c r="I25" s="84"/>
       <c r="J25" s="31"/>
-      <c r="K25" s="84"/>
+      <c r="K25" s="84" t="s">
+        <v>596</v>
+      </c>
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
       <c r="N25" s="84"/>
@@ -10520,10 +10620,10 @@
       <c r="X25" s="86"/>
       <c r="Y25" s="87"/>
       <c r="Z25" s="43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA25" s="88" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB25" s="89"/>
       <c r="AC25" s="90" t="s">
@@ -10561,7 +10661,9 @@
       <c r="H26" s="84"/>
       <c r="I26" s="84"/>
       <c r="J26" s="31"/>
-      <c r="K26" s="84"/>
+      <c r="K26" s="84" t="s">
+        <v>596</v>
+      </c>
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
       <c r="N26" s="84"/>
@@ -10618,7 +10720,9 @@
       <c r="H27" s="84"/>
       <c r="I27" s="84"/>
       <c r="J27" s="31"/>
-      <c r="K27" s="84"/>
+      <c r="K27" s="84" t="s">
+        <v>596</v>
+      </c>
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
       <c r="N27" s="84"/>
@@ -10677,7 +10781,9 @@
       <c r="H28" s="84"/>
       <c r="I28" s="84"/>
       <c r="J28" s="31"/>
-      <c r="K28" s="84"/>
+      <c r="K28" s="84" t="s">
+        <v>596</v>
+      </c>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
       <c r="N28" s="84"/>
@@ -10754,10 +10860,10 @@
       <c r="AB29" s="102"/>
       <c r="AC29" s="103"/>
       <c r="AD29" s="43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AE29" s="104" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AF29" s="105"/>
       <c r="AG29" s="106" t="s">
@@ -13556,7 +13662,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q155"/>
+  <dimension ref="A1:Q160"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -13656,7 +13762,7 @@
         <v>174</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -13667,274 +13773,276 @@
         <v>175</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>589</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="160" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B6" s="159" t="s">
         <v>177</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="H6" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="160" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B7" s="159" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="160" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="B9" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="H9" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B10" t="s">
         <v>183</v>
       </c>
-      <c r="B9" t="s">
+      <c r="H10" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>215</v>
-      </c>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="K11" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="160" t="s">
         <v>189</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="160" t="s">
+      <c r="B13" s="159" t="s">
         <v>190</v>
       </c>
-      <c r="B12" s="159" t="s">
+      <c r="H13" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B16" t="s">
-        <v>201</v>
+        <v>136</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="B17" t="s">
+        <v>200</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15" t="s">
+      <c r="B22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B23" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="K23" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H24" s="2"/>
       <c r="K24" s="2" t="s">
@@ -13943,10 +14051,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H25" s="2"/>
       <c r="K25" s="2" t="s">
@@ -13955,10 +14063,10 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H26" s="2"/>
       <c r="K26" s="2" t="s">
@@ -13967,10 +14075,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -13978,77 +14086,77 @@
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B28" t="s">
-        <v>235</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K28" s="2"/>
+      <c r="A28" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>121</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>227</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B31" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="K32" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="B32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>243</v>
@@ -14059,441 +14167,441 @@
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" t="s">
-        <v>237</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K34" s="2"/>
+      <c r="A34" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K35" s="2"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A38" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B38" s="23" t="s">
+      <c r="C39" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="K39" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="2"/>
-      <c r="K38" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="15" t="s">
+      <c r="C40" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>538</v>
-      </c>
+      <c r="B41" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="22" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="22" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>262</v>
+        <v>315</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="22" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>318</v>
+        <v>316</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="15" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A48" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>536</v>
-      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="22" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="22" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="15" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="D52" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>536</v>
-      </c>
+      <c r="B52" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D53" s="2">
         <v>0.5</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>269</v>
+      <c r="A54" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>261</v>
       </c>
       <c r="D54" s="2">
         <v>0.5</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>271</v>
+      <c r="K54" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>536</v>
+      <c r="A55" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="22" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="22" t="s">
-        <v>273</v>
+        <v>167</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="C58" s="25"/>
+        <v>322</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>261</v>
+      </c>
       <c r="K58" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="22" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C59" s="25"/>
       <c r="K59" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>305</v>
+      <c r="A60" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="C60" s="25"/>
+      <c r="K60" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A62" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>536</v>
+      <c r="B62" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="22" t="s">
-        <v>275</v>
+        <v>155</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="C63" s="25"/>
+        <v>325</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>261</v>
+      </c>
       <c r="K63" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C64" s="25"/>
       <c r="K64" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
@@ -14501,596 +14609,591 @@
         <v>276</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C65" s="25"/>
       <c r="K65" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C66" s="25"/>
       <c r="K66" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A67" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" t="s">
-        <v>331</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>302</v>
+      <c r="A67" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" s="25"/>
+      <c r="K67" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" t="s">
+        <v>332</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B70" t="s">
-        <v>334</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A71" s="150" t="s">
-        <v>133</v>
-      </c>
-      <c r="B71" s="151" t="s">
-        <v>544</v>
-      </c>
-      <c r="C71" s="152" t="s">
-        <v>262</v>
-      </c>
-      <c r="H71" s="2"/>
-      <c r="K71" s="2" t="s">
-        <v>536</v>
+      <c r="B71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="150" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B72" s="151" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C72" s="152" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="15" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A73" s="150" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="151" t="s">
+        <v>544</v>
+      </c>
+      <c r="C73" s="152" t="s">
+        <v>261</v>
+      </c>
+      <c r="H73" s="2"/>
+      <c r="K73" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A74" s="150" t="s">
+        <v>596</v>
+      </c>
+      <c r="B74" s="151" t="s">
+        <v>597</v>
+      </c>
+      <c r="C74" s="152" t="s">
+        <v>261</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="K74" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B73" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
-      <c r="N73" s="17"/>
-      <c r="O73" s="17"/>
-      <c r="P73" s="17"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A74" s="4" t="s">
+      <c r="B75" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
+      <c r="N75" s="17"/>
+      <c r="O75" s="17"/>
+      <c r="P75" s="17"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A75" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A76" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="H76" s="2"/>
-      <c r="K76" s="2" t="s">
-        <v>538</v>
+      <c r="C76" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A78" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>346</v>
+      <c r="A78" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="H78" s="2"/>
+      <c r="K78" s="2" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="15" t="s">
+      <c r="B83" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B84" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17"/>
+      <c r="N84" s="17"/>
+      <c r="O84" s="17"/>
+      <c r="P84" s="17"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A85" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="17"/>
-      <c r="L82" s="17"/>
-      <c r="N82" s="17"/>
-      <c r="O82" s="17"/>
-      <c r="P82" s="17"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A83" s="22" t="s">
+      <c r="B85" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="B83" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A84" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="B84" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A85" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="B85" t="s">
-        <v>356</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="K85" s="2"/>
+      <c r="K85" s="2" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="B86" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B87" t="s">
+        <v>355</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A88" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A89" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="B86" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A87" s="22" t="s">
+      <c r="B89" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="B87" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A88" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A89" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="K89" s="2"/>
+      <c r="K89" s="2" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="15" t="s">
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="17"/>
-      <c r="N91" s="17"/>
-      <c r="O91" s="17"/>
-      <c r="P91" s="17"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A92" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="B92" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A93" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="B93" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>546</v>
-      </c>
+      <c r="B93" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+      <c r="L93" s="17"/>
+      <c r="N93" s="17"/>
+      <c r="O93" s="17"/>
+      <c r="P93" s="17"/>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="22" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="22" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="22" t="s">
-        <v>373</v>
-      </c>
-      <c r="B96" s="23" t="s">
-        <v>380</v>
+        <v>254</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>310</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="22" t="s">
-        <v>381</v>
-      </c>
-      <c r="B97" s="23" t="s">
-        <v>383</v>
+        <v>255</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>311</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="22" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="22" t="s">
-        <v>569</v>
+        <v>380</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="22" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="22" t="s">
-        <v>411</v>
+        <v>568</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A103" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="B103" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="B102" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A103" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B103" t="s">
-        <v>376</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>565</v>
+      <c r="K103" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A104" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B104" t="s">
-        <v>378</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>566</v>
+      <c r="A104" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B105" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B106" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A107" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="H107" s="21" t="s">
-        <v>570</v>
+      <c r="A107" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B107" t="s">
+        <v>376</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A108" s="134" t="s">
-        <v>417</v>
-      </c>
-      <c r="B108" s="135" t="s">
-        <v>452</v>
-      </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="136" t="s">
-        <v>483</v>
+      <c r="A108" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B108" t="s">
+        <v>378</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A109" s="134" t="s">
-        <v>418</v>
-      </c>
-      <c r="B109" s="135" t="s">
-        <v>453</v>
-      </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="136" t="s">
-        <v>484</v>
+      <c r="A109" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="H109" s="21" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="134" t="s">
-        <v>419</v>
-      </c>
-      <c r="B110" s="158" t="s">
-        <v>454</v>
+        <v>416</v>
+      </c>
+      <c r="B110" s="135" t="s">
+        <v>451</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
@@ -15098,15 +15201,15 @@
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
       <c r="H110" s="136" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="134" t="s">
-        <v>420</v>
-      </c>
-      <c r="B111" s="158" t="s">
-        <v>455</v>
+        <v>417</v>
+      </c>
+      <c r="B111" s="135" t="s">
+        <v>452</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
@@ -15114,15 +15217,15 @@
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
       <c r="H111" s="136" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="134" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B112" s="158" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="7"/>
@@ -15130,15 +15233,15 @@
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
       <c r="H112" s="136" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="134" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B113" s="158" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
@@ -15146,15 +15249,15 @@
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="136" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="134" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B114" s="158" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
@@ -15162,15 +15265,15 @@
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
       <c r="H114" s="136" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="134" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B115" s="158" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
@@ -15178,15 +15281,15 @@
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="136" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="134" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B116" s="158" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="7"/>
@@ -15194,15 +15297,15 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="136" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="134" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B117" s="158" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
@@ -15210,15 +15313,15 @@
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
       <c r="H117" s="136" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="134" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B118" s="158" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="7"/>
@@ -15226,69 +15329,69 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="136" t="s">
-        <v>571</v>
+        <v>491</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A119" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B119" s="137" t="s">
-        <v>405</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>197</v>
-      </c>
+      <c r="A119" s="134" t="s">
+        <v>425</v>
+      </c>
+      <c r="B119" s="158" t="s">
+        <v>460</v>
+      </c>
+      <c r="C119" s="8"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
-      <c r="H119" s="138" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="139" t="s">
-        <v>428</v>
-      </c>
-      <c r="B120" s="140" t="s">
-        <v>463</v>
-      </c>
-      <c r="C120" s="11"/>
-      <c r="H120" s="141" t="s">
-        <v>573</v>
-      </c>
-      <c r="I120" s="11"/>
-      <c r="J120" s="11"/>
-      <c r="O120" s="11"/>
-      <c r="P120" s="11"/>
-    </row>
-    <row r="121" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="139" t="s">
-        <v>429</v>
-      </c>
-      <c r="B121" s="140" t="s">
-        <v>464</v>
-      </c>
-      <c r="C121" s="11"/>
-      <c r="H121" s="141" t="s">
-        <v>494</v>
-      </c>
-      <c r="I121" s="11"/>
-      <c r="J121" s="11"/>
-      <c r="O121" s="11"/>
-      <c r="P121" s="11"/>
+      <c r="H119" s="136" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A120" s="134" t="s">
+        <v>426</v>
+      </c>
+      <c r="B120" s="158" t="s">
+        <v>461</v>
+      </c>
+      <c r="C120" s="8"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="136" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" s="137" t="s">
+        <v>404</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="138" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="122" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="139" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B122" s="140" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C122" s="11"/>
       <c r="H122" s="141" t="s">
-        <v>495</v>
+        <v>572</v>
       </c>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
@@ -15297,14 +15400,14 @@
     </row>
     <row r="123" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="139" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B123" s="140" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C123" s="11"/>
       <c r="H123" s="141" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I123" s="11"/>
       <c r="J123" s="11"/>
@@ -15313,14 +15416,14 @@
     </row>
     <row r="124" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="139" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B124" s="140" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C124" s="11"/>
       <c r="H124" s="141" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
@@ -15329,14 +15432,14 @@
     </row>
     <row r="125" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="139" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B125" s="140" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C125" s="11"/>
       <c r="H125" s="141" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I125" s="11"/>
       <c r="J125" s="11"/>
@@ -15345,14 +15448,14 @@
     </row>
     <row r="126" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="139" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B126" s="140" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C126" s="11"/>
       <c r="H126" s="141" t="s">
-        <v>577</v>
+        <v>496</v>
       </c>
       <c r="I126" s="11"/>
       <c r="J126" s="11"/>
@@ -15361,14 +15464,14 @@
     </row>
     <row r="127" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="139" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B127" s="140" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C127" s="11"/>
       <c r="H127" s="141" t="s">
-        <v>574</v>
+        <v>497</v>
       </c>
       <c r="I127" s="11"/>
       <c r="J127" s="11"/>
@@ -15377,14 +15480,14 @@
     </row>
     <row r="128" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="139" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B128" s="140" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C128" s="11"/>
       <c r="H128" s="141" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
@@ -15393,14 +15496,14 @@
     </row>
     <row r="129" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="139" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B129" s="140" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C129" s="11"/>
       <c r="H129" s="141" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
@@ -15408,65 +15511,65 @@
       <c r="P129" s="11"/>
     </row>
     <row r="130" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B130" s="142" t="s">
-        <v>406</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H130" s="11" t="s">
-        <v>578</v>
+      <c r="A130" s="139" t="s">
+        <v>435</v>
+      </c>
+      <c r="B130" s="140" t="s">
+        <v>470</v>
+      </c>
+      <c r="C130" s="11"/>
+      <c r="H130" s="141" t="s">
+        <v>574</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
       <c r="O130" s="11"/>
       <c r="P130" s="11"/>
     </row>
-    <row r="131" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="143" t="s">
-        <v>438</v>
-      </c>
-      <c r="B131" s="144" t="s">
-        <v>473</v>
-      </c>
-      <c r="C131" s="145"/>
-      <c r="H131" s="147" t="s">
-        <v>579</v>
-      </c>
-      <c r="I131" s="145"/>
-      <c r="J131" s="145"/>
-      <c r="O131" s="145"/>
-      <c r="P131" s="145"/>
-    </row>
-    <row r="132" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="143" t="s">
-        <v>439</v>
-      </c>
-      <c r="B132" s="144" t="s">
-        <v>474</v>
-      </c>
-      <c r="C132" s="145"/>
-      <c r="H132" s="147" t="s">
-        <v>580</v>
-      </c>
-      <c r="I132" s="145"/>
-      <c r="J132" s="145"/>
-      <c r="O132" s="145"/>
-      <c r="P132" s="145"/>
+    <row r="131" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="139" t="s">
+        <v>436</v>
+      </c>
+      <c r="B131" s="140" t="s">
+        <v>471</v>
+      </c>
+      <c r="C131" s="11"/>
+      <c r="H131" s="141" t="s">
+        <v>575</v>
+      </c>
+      <c r="I131" s="11"/>
+      <c r="J131" s="11"/>
+      <c r="O131" s="11"/>
+      <c r="P131" s="11"/>
+    </row>
+    <row r="132" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B132" s="142" t="s">
+        <v>405</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="I132" s="11"/>
+      <c r="J132" s="11"/>
+      <c r="O132" s="11"/>
+      <c r="P132" s="11"/>
     </row>
     <row r="133" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="143" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B133" s="144" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C133" s="145"/>
       <c r="H133" s="147" t="s">
-        <v>499</v>
+        <v>578</v>
       </c>
       <c r="I133" s="145"/>
       <c r="J133" s="145"/>
@@ -15475,14 +15578,14 @@
     </row>
     <row r="134" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="143" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B134" s="144" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C134" s="145"/>
       <c r="H134" s="147" t="s">
-        <v>500</v>
+        <v>579</v>
       </c>
       <c r="I134" s="145"/>
       <c r="J134" s="145"/>
@@ -15491,14 +15594,14 @@
     </row>
     <row r="135" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="143" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B135" s="144" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C135" s="145"/>
       <c r="H135" s="147" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="I135" s="145"/>
       <c r="J135" s="145"/>
@@ -15507,14 +15610,14 @@
     </row>
     <row r="136" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="143" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B136" s="144" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C136" s="145"/>
       <c r="H136" s="147" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I136" s="145"/>
       <c r="J136" s="145"/>
@@ -15523,14 +15626,14 @@
     </row>
     <row r="137" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="143" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B137" s="144" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C137" s="145"/>
       <c r="H137" s="147" t="s">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="I137" s="145"/>
       <c r="J137" s="145"/>
@@ -15539,14 +15642,14 @@
     </row>
     <row r="138" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="143" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B138" s="144" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C138" s="145"/>
       <c r="H138" s="147" t="s">
-        <v>584</v>
+        <v>501</v>
       </c>
       <c r="I138" s="145"/>
       <c r="J138" s="145"/>
@@ -15555,14 +15658,14 @@
     </row>
     <row r="139" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="143" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B139" s="144" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C139" s="145"/>
       <c r="H139" s="147" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I139" s="145"/>
       <c r="J139" s="145"/>
@@ -15571,249 +15674,331 @@
     </row>
     <row r="140" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="143" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B140" s="144" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C140" s="145"/>
       <c r="H140" s="147" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I140" s="145"/>
       <c r="J140" s="145"/>
       <c r="O140" s="145"/>
       <c r="P140" s="145"/>
     </row>
-    <row r="141" spans="1:16" s="146" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="148" t="s">
-        <v>127</v>
-      </c>
-      <c r="B141" s="149" t="s">
-        <v>407</v>
-      </c>
-      <c r="C141" s="145" t="s">
-        <v>197</v>
-      </c>
-      <c r="H141" s="144" t="s">
-        <v>581</v>
+    <row r="141" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="143" t="s">
+        <v>445</v>
+      </c>
+      <c r="B141" s="144" t="s">
+        <v>480</v>
+      </c>
+      <c r="C141" s="145"/>
+      <c r="H141" s="147" t="s">
+        <v>582</v>
       </c>
       <c r="I141" s="145"/>
       <c r="J141" s="145"/>
       <c r="O141" s="145"/>
       <c r="P141" s="145"/>
     </row>
-    <row r="142" spans="1:16" s="157" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="154" t="s">
+    <row r="142" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="143" t="s">
+        <v>446</v>
+      </c>
+      <c r="B142" s="144" t="s">
+        <v>481</v>
+      </c>
+      <c r="C142" s="145"/>
+      <c r="H142" s="147" t="s">
+        <v>581</v>
+      </c>
+      <c r="I142" s="145"/>
+      <c r="J142" s="145"/>
+      <c r="O142" s="145"/>
+      <c r="P142" s="145"/>
+    </row>
+    <row r="143" spans="1:16" s="146" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="148" t="s">
+        <v>127</v>
+      </c>
+      <c r="B143" s="149" t="s">
+        <v>406</v>
+      </c>
+      <c r="C143" s="145" t="s">
+        <v>196</v>
+      </c>
+      <c r="H143" s="144" t="s">
+        <v>580</v>
+      </c>
+      <c r="I143" s="145"/>
+      <c r="J143" s="145"/>
+      <c r="O143" s="145"/>
+      <c r="P143" s="145"/>
+    </row>
+    <row r="144" spans="1:16" s="157" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="B142" s="155" t="s">
-        <v>408</v>
-      </c>
-      <c r="C142" s="156" t="s">
-        <v>197</v>
-      </c>
-      <c r="H142" s="156" t="s">
-        <v>448</v>
-      </c>
-      <c r="I142" s="156"/>
-      <c r="J142" s="156"/>
-      <c r="O142" s="156"/>
-      <c r="P142" s="156"/>
-    </row>
-    <row r="143" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="15" t="s">
+      <c r="B144" s="155" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" s="156" t="s">
+        <v>196</v>
+      </c>
+      <c r="H144" s="156" t="s">
+        <v>447</v>
+      </c>
+      <c r="I144" s="156"/>
+      <c r="J144" s="156"/>
+      <c r="O144" s="156"/>
+      <c r="P144" s="156"/>
+    </row>
+    <row r="145" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B143" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="C143" s="17"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
-      <c r="G143" s="17"/>
-      <c r="I143" s="17"/>
-      <c r="J143" s="17"/>
-      <c r="K143" s="17"/>
-      <c r="L143" s="17"/>
-      <c r="N143" s="17"/>
-      <c r="O143" s="17"/>
-      <c r="P143" s="17"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A144" s="150" t="s">
+      <c r="B145" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="C145" s="17"/>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="17"/>
+      <c r="G145" s="17"/>
+      <c r="I145" s="17"/>
+      <c r="J145" s="17"/>
+      <c r="K145" s="17"/>
+      <c r="L145" s="17"/>
+      <c r="N145" s="17"/>
+      <c r="O145" s="17"/>
+      <c r="P145" s="17"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A146" s="150" t="s">
+        <v>401</v>
+      </c>
+      <c r="B146" s="151" t="s">
+        <v>506</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A147" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B144" s="151" t="s">
+      <c r="B147" t="s">
+        <v>502</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A148" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B149" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="K144" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A145" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="B145" t="s">
-        <v>503</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A146" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B147" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="C147" s="17"/>
-      <c r="D147" s="17"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="17"/>
-      <c r="G147" s="17"/>
-      <c r="I147" s="17"/>
-      <c r="J147" s="17"/>
-      <c r="K147" s="17"/>
-      <c r="L147" s="17"/>
-      <c r="N147" s="17"/>
-      <c r="O147" s="17"/>
-      <c r="P147" s="17"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A148" s="150" t="s">
+      <c r="C149" s="17"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="17"/>
+      <c r="G149" s="17"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+      <c r="L149" s="17"/>
+      <c r="N149" s="17"/>
+      <c r="O149" s="17"/>
+      <c r="P149" s="17"/>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A150" s="150" t="s">
         <v>160</v>
       </c>
-      <c r="B148" s="153" t="s">
+      <c r="B150" s="153" t="s">
+        <v>449</v>
+      </c>
+      <c r="C150" s="152" t="s">
+        <v>261</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="150" t="s">
+        <v>147</v>
+      </c>
+      <c r="B151" s="153" t="s">
         <v>450</v>
       </c>
-      <c r="C148" s="152" t="s">
-        <v>262</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="150" t="s">
-        <v>147</v>
-      </c>
-      <c r="B149" s="153" t="s">
-        <v>451</v>
-      </c>
-      <c r="C149" s="152" t="s">
-        <v>262</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="150" t="s">
+      <c r="C151" s="152" t="s">
+        <v>261</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="150" t="s">
+        <v>521</v>
+      </c>
+      <c r="B152" s="153" t="s">
         <v>522</v>
       </c>
-      <c r="B150" s="153" t="s">
-        <v>523</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A151" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B151" t="s">
-        <v>521</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A152" s="150" t="s">
-        <v>524</v>
-      </c>
-      <c r="B152" s="153" t="s">
-        <v>525</v>
-      </c>
       <c r="K152" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B153" s="159" t="s">
-        <v>526</v>
+        <v>145</v>
+      </c>
+      <c r="B153" t="s">
+        <v>520</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>530</v>
+        <v>585</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="150" t="s">
-        <v>587</v>
+        <v>523</v>
       </c>
       <c r="B154" s="153" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B155" s="159" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>529</v>
       </c>
     </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A156" s="150" t="s">
+        <v>586</v>
+      </c>
+      <c r="B156" s="153" t="s">
+        <v>526</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A157" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B157" s="159" t="s">
+        <v>527</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B158" s="162" t="s">
+        <v>542</v>
+      </c>
+      <c r="C158" s="163"/>
+      <c r="D158" s="163"/>
+      <c r="E158" s="163"/>
+      <c r="F158" s="163"/>
+      <c r="G158" s="163"/>
+      <c r="I158" s="163"/>
+      <c r="J158" s="163"/>
+      <c r="K158" s="163"/>
+      <c r="L158" s="163"/>
+      <c r="N158" s="163"/>
+      <c r="O158" s="163"/>
+      <c r="P158" s="163"/>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A159" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B159" t="s">
+        <v>598</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A160" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B160" t="s">
+        <v>593</v>
+      </c>
+      <c r="H160" s="164" t="s">
+        <v>595</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K1048576">
-    <cfRule type="expression" dxfId="4" priority="2">
+  <conditionalFormatting sqref="K2:K158 K161:K1048576">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(L2&lt;&gt;"",NOT(K2&lt;&gt;""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K159">
+    <cfRule type="expression" dxfId="0" priority="15">
+      <formula>AND(L160&lt;&gt;"",NOT(K159&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{3C5E5528-F961-4CFC-83ED-CB90A50DF965}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:P1048576 I2:I1048576" xr:uid="{7CB7BECB-8CCA-402C-8209-B57AEC65D6EC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576 O2:P1048576" xr:uid="{7CB7BECB-8CCA-402C-8209-B57AEC65D6EC}">
       <formula1>"n,y"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7B357739-ECEB-45D0-9FF6-C94815526279}">
@@ -15842,23 +16027,36 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K2:K1048576</xm:sqref>
+          <xm:sqref>K2:K158 K161:K1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="14" id="{BE3DBFB1-F6C9-4726-B787-A3DD602656FE}">
+            <xm:f>AND(K159&lt;&gt;"",ISERROR(MATCH(K159,'Databook Pages'!$A:$A,0)))</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K159</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0E7D17F-9C98-4BBD-89E8-B63866BAA65B}">
-          <x14:formula1>
-            <xm:f>'Databook Pages'!$A$2:$A$9999</xm:f>
-          </x14:formula1>
-          <xm:sqref>K1:K1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5BACFCF-5A80-4E38-B286-225138198031}">
           <x14:formula1>
             <xm:f>'Population types'!$A$2:$A$9999</xm:f>
           </x14:formula1>
           <xm:sqref>N1:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0E7D17F-9C98-4BBD-89E8-B63866BAA65B}">
+          <x14:formula1>
+            <xm:f>'Databook Pages'!$A$2:$A$9999</xm:f>
+          </x14:formula1>
+          <xm:sqref>K161:K1048576 K1:K159</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15927,13 +16125,13 @@
     </row>
     <row r="2" spans="1:12" s="19" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>217</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>218</v>
       </c>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -15942,7 +16140,7 @@
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I2" s="21"/>
       <c r="J2" s="21"/>
@@ -15950,13 +16148,13 @@
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>281</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>282</v>
       </c>
       <c r="D3" s="2"/>
       <c r="F3" s="21">
@@ -15965,33 +16163,33 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" t="s">
         <v>283</v>
       </c>
-      <c r="B4" t="s">
-        <v>284</v>
-      </c>
       <c r="C4" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F4" s="21">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F5" s="21">
         <v>0</v>
@@ -15999,13 +16197,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F6" s="21">
         <v>0</v>
@@ -16013,33 +16211,33 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B7" t="s">
         <v>559</v>
       </c>
-      <c r="B7" t="s">
-        <v>560</v>
-      </c>
       <c r="C7" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F7" s="21">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F8" s="21">
         <v>0</v>
@@ -16047,33 +16245,33 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>560</v>
+      </c>
+      <c r="B9" t="s">
         <v>561</v>
       </c>
-      <c r="B9" t="s">
-        <v>562</v>
-      </c>
       <c r="C9" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10" s="21">
         <v>0</v>
@@ -16081,16 +16279,16 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F11" s="21">
         <v>0</v>
@@ -16098,16 +16296,16 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F12" s="21">
         <v>0</v>
@@ -16115,16 +16313,16 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -16132,16 +16330,16 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B14" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F14" s="21">
         <v>0</v>
@@ -16149,13 +16347,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" t="s">
         <v>517</v>
       </c>
-      <c r="B15" t="s">
-        <v>518</v>
-      </c>
       <c r="C15" s="20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D15" s="2"/>
       <c r="F15" s="21">
@@ -16164,16 +16362,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F16" s="21">
         <v>0</v>
@@ -16181,13 +16379,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>518</v>
+      </c>
+      <c r="B17" t="s">
         <v>519</v>
       </c>
-      <c r="B17" t="s">
-        <v>520</v>
-      </c>
       <c r="C17" s="20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D17" s="2"/>
       <c r="F17" s="21">
@@ -16196,16 +16394,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F18" s="21">
         <v>0</v>
@@ -16213,33 +16411,33 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B19" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F19" s="21">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B20" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F20" s="21">
         <v>0</v>
@@ -16247,13 +16445,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B21" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -16261,13 +16459,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F22" s="21">
         <v>0</v>
@@ -16275,32 +16473,32 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B23" t="s">
+        <v>553</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F23" s="21">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AND(A2&lt;&gt;"",NOT(B2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND(I2&lt;&gt;"",NOT(H2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16379,10 +16577,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B2" t="s">
         <v>384</v>
-      </c>
-      <c r="B2" t="s">
-        <v>385</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -16396,10 +16594,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B3" t="s">
         <v>386</v>
-      </c>
-      <c r="B3" t="s">
-        <v>387</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -16414,7 +16612,7 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16454,26 +16652,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CDFBE7-8648-40E2-A2CE-578266086F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DEDFF-6BC8-4624-B8A5-71EA1AC2599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="2100" windowWidth="19380" windowHeight="10380" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -6586,7 +6586,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6626,20 +6633,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7151,7 +7144,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7644,12 +7637,12 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>AND(I2&lt;&gt;"",NOT(H2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13844,10 +13837,10 @@
       <c r="B9" s="159" t="s">
         <v>181</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
@@ -15982,7 +15975,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15992,7 +15985,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K159">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="4" priority="15">
       <formula>AND(L160&lt;&gt;"",NOT(K159&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16027,20 +16020,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K2:K158 K161:K1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="14" id="{BE3DBFB1-F6C9-4726-B787-A3DD602656FE}">
-            <xm:f>AND(K159&lt;&gt;"",ISERROR(MATCH(K159,'Databook Pages'!$A:$A,0)))</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K159</xm:sqref>
+          <xm:sqref>K2:K159 K161:K1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -16493,12 +16473,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>AND(A2&lt;&gt;"",NOT(B2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H1048576">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>AND(I2&lt;&gt;"",NOT(H2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16612,7 +16592,7 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DEDFF-6BC8-4624-B8A5-71EA1AC2599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E1A759-0FF2-46D2-8A61-48C8DACD2224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -5381,12 +5381,6 @@
     <t>Annual Rate of Hepatitis B treatment (model fit)</t>
   </si>
   <si>
-    <t xml:space="preserve">sdiv(max((hepb_pop*treat_measure)-treated, 0), ltc_n) </t>
-  </si>
-  <si>
-    <t>max(sdiv(max((hepb_pop*ltc_measure)-ltc_n, 0), diag_n) - anc_ltc_rate, 0)</t>
-  </si>
-  <si>
     <t>compensated</t>
   </si>
   <si>
@@ -5483,9 +5477,6 @@
     <t>HBeAg positive HepB (of all)</t>
   </si>
   <si>
-    <t>diag_epos, undiag_epos</t>
-  </si>
-  <si>
     <t>hcc, hcc_d, hcc_l, hcc_t</t>
   </si>
   <si>
@@ -5526,9 +5517,6 @@
   </si>
   <si>
     <t>hepbd_cov</t>
-  </si>
-  <si>
-    <t>sdiv(b_rate*hepbd_cov -(b_rate*(mprev_diag_epos+mprev_diag_eneg) + b_rate*(mprev_undiag_epos+mprev_undiag_eneg)*anc_scr), b_rate*hepbd_cov)</t>
   </si>
   <si>
     <t>b_rate*(hepb3_cov*ve_hepb3)*(1-(mprev_diag_epos+mprev_diag_eneg+mprev_undiag_epos+mprev_undiag_eneg))</t>
@@ -5631,6 +5619,18 @@
   </si>
   <si>
     <t>hep_dth</t>
+  </si>
+  <si>
+    <t>max(sdiv(max((hepb_pop*ltc_measure)-ltc_n, 0) * (diag_n&gt;0), diag_n) - anc_ltc_rate, 0)</t>
+  </si>
+  <si>
+    <t>sdiv(max((hepb_pop*treat_measure)-treated, 0) * (ltc_n&gt;0), ltc_n)</t>
+  </si>
+  <si>
+    <t>sdiv((b_rate*hepbd_cov -(b_rate*(mprev_diag_epos+mprev_diag_eneg) + b_rate*(mprev_undiag_epos+mprev_undiag_eneg)*anc_scr)) * (hepbd_cov&gt;0), b_rate*hepbd_cov)</t>
+  </si>
+  <si>
+    <t>ei_d,ei_l,ei_t,eh_d,eh_l,eh_t, ei,eh</t>
   </si>
 </sst>
 </file>
@@ -7088,58 +7088,58 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B8" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B10" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +9902,7 @@
       <c r="I13" s="40"/>
       <c r="J13" s="31"/>
       <c r="K13" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L13" s="41"/>
       <c r="M13" s="42"/>
@@ -9961,7 +9961,7 @@
       <c r="I14" s="40"/>
       <c r="J14" s="31"/>
       <c r="K14" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L14" s="41"/>
       <c r="M14" s="48"/>
@@ -10018,7 +10018,7 @@
       <c r="I15" s="40"/>
       <c r="J15" s="31"/>
       <c r="K15" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L15" s="41"/>
       <c r="M15" s="48"/>
@@ -10124,7 +10124,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
       <c r="K17" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L17" s="30"/>
       <c r="M17" s="55"/>
@@ -10185,7 +10185,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="31"/>
       <c r="K18" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
@@ -10244,7 +10244,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="31"/>
       <c r="K19" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
@@ -10305,7 +10305,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="31"/>
       <c r="K20" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
@@ -10364,7 +10364,7 @@
       <c r="I21" s="34"/>
       <c r="J21" s="31"/>
       <c r="K21" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
@@ -10423,7 +10423,7 @@
       <c r="I22" s="34"/>
       <c r="J22" s="31"/>
       <c r="K22" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
@@ -10480,7 +10480,7 @@
       <c r="I23" s="34"/>
       <c r="J23" s="31"/>
       <c r="K23" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
@@ -10539,7 +10539,7 @@
       <c r="I24" s="34"/>
       <c r="J24" s="31"/>
       <c r="K24" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
@@ -10594,7 +10594,7 @@
       <c r="I25" s="84"/>
       <c r="J25" s="31"/>
       <c r="K25" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
@@ -10655,7 +10655,7 @@
       <c r="I26" s="84"/>
       <c r="J26" s="31"/>
       <c r="K26" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
@@ -10714,7 +10714,7 @@
       <c r="I27" s="84"/>
       <c r="J27" s="31"/>
       <c r="K27" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
@@ -10775,7 +10775,7 @@
       <c r="I28" s="84"/>
       <c r="J28" s="31"/>
       <c r="K28" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
@@ -13774,10 +13774,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>212</v>
@@ -13791,7 +13791,7 @@
         <v>177</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="K6" s="2"/>
     </row>
@@ -13806,7 +13806,7 @@
         <v>261</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -14257,7 +14257,7 @@
         <v>228</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K40" s="2"/>
     </row>
@@ -14289,7 +14289,7 @@
         <v>312</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
@@ -14300,7 +14300,7 @@
         <v>313</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
@@ -14311,7 +14311,7 @@
         <v>314</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -14322,7 +14322,7 @@
         <v>315</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -14336,7 +14336,7 @@
         <v>261</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
@@ -14347,7 +14347,7 @@
         <v>317</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14381,7 +14381,7 @@
         <v>261</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
@@ -14392,7 +14392,7 @@
         <v>266</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
@@ -14403,7 +14403,7 @@
         <v>267</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14440,7 +14440,7 @@
         <v>0.5</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
@@ -14457,7 +14457,7 @@
         <v>0.5</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
@@ -14488,7 +14488,7 @@
         <v>261</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
@@ -14502,7 +14502,7 @@
         <v>261</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -14516,7 +14516,7 @@
         <v>261</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="C59" s="25"/>
       <c r="K59" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="C60" s="25"/>
       <c r="K60" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -14582,7 +14582,7 @@
         <v>261</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="C64" s="25"/>
       <c r="K64" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="C65" s="25"/>
       <c r="K65" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="C66" s="25"/>
       <c r="K66" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C67" s="25"/>
       <c r="K67" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
@@ -14686,7 +14686,7 @@
         <v>261</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -14694,14 +14694,14 @@
         <v>133</v>
       </c>
       <c r="B72" s="151" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C72" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
@@ -14709,29 +14709,29 @@
         <v>135</v>
       </c>
       <c r="B73" s="151" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C73" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="150" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B74" s="151" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C74" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="H78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.35">
@@ -14895,7 +14895,7 @@
         <v>351</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.35">
@@ -14906,7 +14906,7 @@
         <v>353</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.35">
@@ -14929,7 +14929,7 @@
         <v>366</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.35">
@@ -14940,7 +14940,7 @@
         <v>359</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
@@ -15013,7 +15013,7 @@
         <v>308</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
@@ -15024,7 +15024,7 @@
         <v>309</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
@@ -15035,7 +15035,7 @@
         <v>310</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
@@ -15046,7 +15046,7 @@
         <v>311</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
@@ -15057,7 +15057,7 @@
         <v>379</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
@@ -15068,7 +15068,7 @@
         <v>382</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
@@ -15079,18 +15079,18 @@
         <v>400</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="22" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B101" s="23" t="s">
         <v>398</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
@@ -15101,7 +15101,7 @@
         <v>409</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
@@ -15112,7 +15112,7 @@
         <v>412</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
@@ -15123,7 +15123,7 @@
         <v>413</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
@@ -15134,7 +15134,7 @@
         <v>375</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
@@ -15145,7 +15145,7 @@
         <v>377</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
@@ -15156,7 +15156,7 @@
         <v>376</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
@@ -15167,7 +15167,7 @@
         <v>378</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
@@ -15178,7 +15178,7 @@
         <v>399</v>
       </c>
       <c r="H109" s="21" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
@@ -15354,7 +15354,7 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="136" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -15372,7 +15372,7 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="138" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="122" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="C122" s="11"/>
       <c r="H122" s="141" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="C128" s="11"/>
       <c r="H128" s="141" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C129" s="11"/>
       <c r="H129" s="141" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C130" s="11"/>
       <c r="H130" s="141" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C131" s="11"/>
       <c r="H131" s="141" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
@@ -15546,7 +15546,7 @@
         <v>196</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I132" s="11"/>
       <c r="J132" s="11"/>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="C133" s="145"/>
       <c r="H133" s="147" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="I133" s="145"/>
       <c r="J133" s="145"/>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C134" s="145"/>
       <c r="H134" s="147" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="I134" s="145"/>
       <c r="J134" s="145"/>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="C139" s="145"/>
       <c r="H139" s="147" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I139" s="145"/>
       <c r="J139" s="145"/>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="C140" s="145"/>
       <c r="H140" s="147" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I140" s="145"/>
       <c r="J140" s="145"/>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="C141" s="145"/>
       <c r="H141" s="147" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I141" s="145"/>
       <c r="J141" s="145"/>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C142" s="145"/>
       <c r="H142" s="147" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="I142" s="145"/>
       <c r="J142" s="145"/>
@@ -15724,7 +15724,7 @@
         <v>196</v>
       </c>
       <c r="H143" s="144" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I143" s="145"/>
       <c r="J143" s="145"/>
@@ -15777,7 +15777,7 @@
         <v>506</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.35">
@@ -15836,7 +15836,7 @@
         <v>261</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -15850,7 +15850,7 @@
         <v>261</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -15861,7 +15861,7 @@
         <v>522</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.35">
@@ -15875,7 +15875,7 @@
         <v>261</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.35">
@@ -15886,7 +15886,7 @@
         <v>524</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
@@ -15900,18 +15900,18 @@
         <v>261</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>529</v>
+        <v>596</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="150" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B156" s="153" t="s">
         <v>526</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.35">
@@ -15925,7 +15925,7 @@
         <v>261</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>528</v>
+        <v>597</v>
       </c>
     </row>
     <row r="158" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -15933,7 +15933,7 @@
         <v>171</v>
       </c>
       <c r="B158" s="162" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C158" s="163"/>
       <c r="D158" s="163"/>
@@ -15950,27 +15950,27 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B159" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B160" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="H160" s="164" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -16158,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -16191,10 +16191,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>285</v>
@@ -16206,7 +16206,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -16225,10 +16225,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B9" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>286</v>
@@ -16240,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -16313,7 +16313,7 @@
         <v>397</v>
       </c>
       <c r="B14" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>392</v>
@@ -16406,18 +16406,18 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F20" s="21">
         <v>0</v>
@@ -16425,13 +16425,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B21" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -16439,13 +16439,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B22" t="s">
+        <v>550</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F22" s="21">
         <v>0</v>
@@ -16453,13 +16453,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>554</v>
+        <v>599</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>279</v>
@@ -16468,7 +16468,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="603">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -5631,6 +5631,15 @@
   </si>
   <si>
     <t>hep_dth</t>
+  </si>
+  <si>
+    <t>max(sdiv(max((hepb_pop*ltc_measure)-ltc_n, 0), max(diag_n, 1)) - anc_ltc_rate, 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdiv(max((hepb_pop*treat_measure)-treated, 0), max(ltc_n, 1)) </t>
+  </si>
+  <si>
+    <t>sdiv(b_rate*hepbd_cov-(b_rate*(mprev_diag_epos+mprev_diag_eneg) + b_rate*(mprev_undiag_epos+mprev_undiag_eneg)*anc_scr), b_rate*hepbd_cov+(1-sdiv(b_rate*hepbd_cov,b_rate*hepbd_cov)))*sdiv(b_rate*hepbd_cov,b_rate*hepbd_cov)</t>
   </si>
 </sst>
 </file>
@@ -15178,7 +15187,7 @@
         <v>399</v>
       </c>
       <c r="H109" s="21" t="s">
-        <v>569</v>
+        <v>602</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
@@ -15900,7 +15909,7 @@
         <v>261</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>529</v>
+        <v>600</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
@@ -15925,7 +15934,7 @@
         <v>261</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>528</v>
+        <v>601</v>
       </c>
     </row>
     <row r="158" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DEDFF-6BC8-4624-B8A5-71EA1AC2599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3139061-44C5-42A6-B9ED-555AB2DC9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="8220" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="692">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -3908,9 +3908,6 @@
     </r>
   </si>
   <si>
-    <t>1-(acu_chb+acu_dth)</t>
-  </si>
-  <si>
     <t>Disease Progression (Natural History)</t>
   </si>
   <si>
@@ -5381,12 +5378,6 @@
     <t>Annual Rate of Hepatitis B treatment (model fit)</t>
   </si>
   <si>
-    <t xml:space="preserve">sdiv(max((hepb_pop*treat_measure)-treated, 0), ltc_n) </t>
-  </si>
-  <si>
-    <t>max(sdiv(max((hepb_pop*ltc_measure)-ltc_n, 0), diag_n) - anc_ltc_rate, 0)</t>
-  </si>
-  <si>
     <t>compensated</t>
   </si>
   <si>
@@ -5528,9 +5519,6 @@
     <t>hepbd_cov</t>
   </si>
   <si>
-    <t>sdiv(b_rate*hepbd_cov -(b_rate*(mprev_diag_epos+mprev_diag_eneg) + b_rate*(mprev_undiag_epos+mprev_undiag_eneg)*anc_scr), b_rate*hepbd_cov)</t>
-  </si>
-  <si>
     <t>b_rate*(hepb3_cov*ve_hepb3)*(1-(mprev_diag_epos+mprev_diag_eneg+mprev_undiag_epos+mprev_undiag_eneg))</t>
   </si>
   <si>
@@ -5640,6 +5628,285 @@
   </si>
   <si>
     <t>sdiv(b_rate*hepbd_cov-(b_rate*(mprev_diag_epos+mprev_diag_eneg) + b_rate*(mprev_undiag_epos+mprev_undiag_eneg)*anc_scr), b_rate*hepbd_cov+(1-sdiv(b_rate*hepbd_cov,b_rate*hepbd_cov)))*sdiv(b_rate*hepbd_cov,b_rate*hepbd_cov)</t>
+  </si>
+  <si>
+    <t>horiz_chb</t>
+  </si>
+  <si>
+    <t>Horizontal Transmission Leading to CHB</t>
+  </si>
+  <si>
+    <t>horiz*acu_chb</t>
+  </si>
+  <si>
+    <t>horiz_acu</t>
+  </si>
+  <si>
+    <t>Horizontal Transmission Leading to Acute HBV</t>
+  </si>
+  <si>
+    <t>horiz*(1-acu_chb)</t>
+  </si>
+  <si>
+    <t>1-acu_dth</t>
+  </si>
+  <si>
+    <t>sh_cost</t>
+  </si>
+  <si>
+    <t>Costs</t>
+  </si>
+  <si>
+    <t>treat_cost</t>
+  </si>
+  <si>
+    <t>diag_cost</t>
+  </si>
+  <si>
+    <t>diag_price</t>
+  </si>
+  <si>
+    <t>treat_price</t>
+  </si>
+  <si>
+    <t>diagnoses</t>
+  </si>
+  <si>
+    <t>Annual number of diagnoses made</t>
+  </si>
+  <si>
+    <t>ei:ei_d+eh:eh_d+si:si_d+sh:sh_d+cc:cc_d+dc:dc_d+hcc:hcc_d</t>
+  </si>
+  <si>
+    <t>Annual cost of hepatitis B diagnoses</t>
+  </si>
+  <si>
+    <t>Estimated price of a hepatitis B diagnosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discounting rate assumed for costs </t>
+  </si>
+  <si>
+    <t>disc_rate_cost</t>
+  </si>
+  <si>
+    <t>chb_ltc_price</t>
+  </si>
+  <si>
+    <t>cc_ltc_price</t>
+  </si>
+  <si>
+    <t>dc_ltc_nt_price</t>
+  </si>
+  <si>
+    <t>dc_ltc_tx_price</t>
+  </si>
+  <si>
+    <t>hcc_ltc_nt_price</t>
+  </si>
+  <si>
+    <t>hcc_ltc_tx_price</t>
+  </si>
+  <si>
+    <t>chb_dm_cost</t>
+  </si>
+  <si>
+    <t>Annual price CHB disease management</t>
+  </si>
+  <si>
+    <t>Annual cost of CHB disease management</t>
+  </si>
+  <si>
+    <t>Annual price of CC disease management</t>
+  </si>
+  <si>
+    <t>cc_dm_cost</t>
+  </si>
+  <si>
+    <t>Annual cost of CC disease management</t>
+  </si>
+  <si>
+    <t>Annual price of DC disease management (not treated)</t>
+  </si>
+  <si>
+    <t>Annual price of HCC disease management (not treated)</t>
+  </si>
+  <si>
+    <t>Annual price of DC disease management (on treatment)</t>
+  </si>
+  <si>
+    <t>dc_dm_cost</t>
+  </si>
+  <si>
+    <t>Annual cost of DC disease management (total)</t>
+  </si>
+  <si>
+    <t>((dc_l*dc_ltc_nt_price)+(dc_t*dc_ltc_tx_price))*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>(cc_l+cc_t)*cc_ltc_price*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>(ei_l+eh_l+si_l+sh_l+ei_t+eh_t+si_t+sh_t)*chb_ltc_price*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>diag_price*diagnoses*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>Annual price of HCC disease management (treated)</t>
+  </si>
+  <si>
+    <t>hcc_dm_cost</t>
+  </si>
+  <si>
+    <t>Annual cost of HCC dsease management (total)</t>
+  </si>
+  <si>
+    <t>((hcc_l*hcc_ltc_nt_price)+(hcc_t*hcc_ltc_tx_price))*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>dm_cost</t>
+  </si>
+  <si>
+    <t>Annual disease management costs</t>
+  </si>
+  <si>
+    <t>chb_dm_cost+cc_dm_cost+dc_dm_cost+hcc_dm_cost</t>
+  </si>
+  <si>
+    <t>Direct Costs of Hepatitis B</t>
+  </si>
+  <si>
+    <t>Placeholder mortality costs</t>
+  </si>
+  <si>
+    <t>stat_year_life</t>
+  </si>
+  <si>
+    <t>Value for a lost statistical year of life in Australia</t>
+  </si>
+  <si>
+    <t>mort_cost</t>
+  </si>
+  <si>
+    <t>Cost of HBV attributable deaths in Australia</t>
+  </si>
+  <si>
+    <t>hep_dth*stat_year_life*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>QALYs</t>
+  </si>
+  <si>
+    <t>direct_costs</t>
+  </si>
+  <si>
+    <t>Total Direct Costs of HepB</t>
+  </si>
+  <si>
+    <t>diag_cost+dm_cost+treat_cost</t>
+  </si>
+  <si>
+    <t>Annual (weighted) price of hepatitis B treatment in Australia</t>
+  </si>
+  <si>
+    <t>Annual cost of hepatitis B treatment</t>
+  </si>
+  <si>
+    <t>treated*treat_price*disc_rate_cost</t>
+  </si>
+  <si>
+    <t>ql_clr</t>
+  </si>
+  <si>
+    <t>ql_chb</t>
+  </si>
+  <si>
+    <t>ql_cc</t>
+  </si>
+  <si>
+    <t>ql_dc</t>
+  </si>
+  <si>
+    <t>ql_hcc</t>
+  </si>
+  <si>
+    <t>disc_rate_qaly</t>
+  </si>
+  <si>
+    <t>QoL Weight: No hepatititis B</t>
+  </si>
+  <si>
+    <t>QoL Weight: CHB</t>
+  </si>
+  <si>
+    <t>QoL Weight: Compensated Cirrhosis</t>
+  </si>
+  <si>
+    <t>QoL Weight: Decompensated Cirrhosis</t>
+  </si>
+  <si>
+    <t>QoL Weight: HCC</t>
+  </si>
+  <si>
+    <t>Discounting rate assumed for QALYs</t>
+  </si>
+  <si>
+    <t>sh_qaly</t>
+  </si>
+  <si>
+    <t>qalys_clr</t>
+  </si>
+  <si>
+    <t>qalys_chb</t>
+  </si>
+  <si>
+    <t>qalys_cc</t>
+  </si>
+  <si>
+    <t>qalys_dc</t>
+  </si>
+  <si>
+    <t>qalys_hcc</t>
+  </si>
+  <si>
+    <t>qalys_total</t>
+  </si>
+  <si>
+    <t>QALYs: No hepatitis B</t>
+  </si>
+  <si>
+    <t>ql_clr*(sus+vax+imm_chb)</t>
+  </si>
+  <si>
+    <t>QALYs: CHB</t>
+  </si>
+  <si>
+    <t>QALYs: HCC</t>
+  </si>
+  <si>
+    <t>QALYs: Compensated Cirrhosis</t>
+  </si>
+  <si>
+    <t>QALYs: Decompensated Cirrhosis</t>
+  </si>
+  <si>
+    <t>QALYs: Total (discounted)</t>
+  </si>
+  <si>
+    <t>ql_chb*(ei+ei_d+ei_l+ei_t+eh+eh_d+eh_l+eh_t+si+si_d+si_l+si_t+sh+sh_d+sh_l+sh_t)</t>
+  </si>
+  <si>
+    <t>ql_cc*compensated</t>
+  </si>
+  <si>
+    <t>ql_dc*decompensated</t>
+  </si>
+  <si>
+    <t>ql_hcc*livercancer</t>
+  </si>
+  <si>
+    <t>(qalys_clr+qalys_chb+qalys_cc+qalys_dc+qalys_hcc)*disc_rate_qaly</t>
   </si>
 </sst>
 </file>
@@ -7056,7 +7323,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" customWidth="1"/>
@@ -7097,58 +7364,74 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B9" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B10" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B11" t="s">
-        <v>548</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>673</v>
+      </c>
+      <c r="B13" t="s">
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -7721,7 +8004,7 @@
     <col min="10" max="10" width="12" style="37" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.1796875" style="32" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.81640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.81640625" style="32"/>
+    <col min="13" max="13" width="10.54296875" style="32" customWidth="1"/>
     <col min="14" max="14" width="15" style="32" customWidth="1"/>
     <col min="15" max="15" width="12" style="32" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="8.81640625" style="32"/>
@@ -9644,7 +9927,7 @@
       <c r="AM7" s="31"/>
       <c r="AN7" s="31"/>
     </row>
-    <row r="8" spans="1:398" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:398" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="26" t="str">
         <f>IF(Compartments!$A8&lt;&gt;"",Compartments!$A8,"")</f>
         <v>sus</v>
@@ -9664,9 +9947,11 @@
       <c r="J8" s="31"/>
       <c r="K8" s="36"/>
       <c r="L8" s="36" t="s">
-        <v>403</v>
-      </c>
-      <c r="M8" s="36"/>
+        <v>602</v>
+      </c>
+      <c r="M8" s="36" t="s">
+        <v>599</v>
+      </c>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
       <c r="P8" s="36"/>
@@ -9861,9 +10146,7 @@
         <v>130</v>
       </c>
       <c r="L12" s="36"/>
-      <c r="M12" s="38" t="s">
-        <v>131</v>
-      </c>
+      <c r="M12" s="38"/>
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
       <c r="P12" s="38"/>
@@ -9911,15 +10194,15 @@
       <c r="I13" s="40"/>
       <c r="J13" s="31"/>
       <c r="K13" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L13" s="41"/>
       <c r="M13" s="42"/>
       <c r="N13" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O13" s="44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P13" s="45"/>
       <c r="Q13" s="46" t="s">
@@ -9970,7 +10253,7 @@
       <c r="I14" s="40"/>
       <c r="J14" s="31"/>
       <c r="K14" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L14" s="41"/>
       <c r="M14" s="48"/>
@@ -10027,7 +10310,7 @@
       <c r="I15" s="40"/>
       <c r="J15" s="31"/>
       <c r="K15" s="40" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L15" s="41"/>
       <c r="M15" s="48"/>
@@ -10133,7 +10416,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
       <c r="K17" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L17" s="30"/>
       <c r="M17" s="55"/>
@@ -10142,10 +10425,10 @@
       <c r="P17" s="56"/>
       <c r="Q17" s="57"/>
       <c r="R17" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S17" s="43" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="T17" s="58"/>
       <c r="U17" s="59" t="s">
@@ -10194,7 +10477,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="31"/>
       <c r="K18" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
@@ -10253,7 +10536,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="31"/>
       <c r="K19" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
@@ -10314,7 +10597,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="31"/>
       <c r="K20" s="30" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
@@ -10373,7 +10656,7 @@
       <c r="I21" s="34"/>
       <c r="J21" s="31"/>
       <c r="K21" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
@@ -10386,10 +10669,10 @@
       <c r="T21" s="70"/>
       <c r="U21" s="71"/>
       <c r="V21" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="W21" s="72" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="X21" s="73"/>
       <c r="Y21" s="74" t="s">
@@ -10432,7 +10715,7 @@
       <c r="I22" s="34"/>
       <c r="J22" s="31"/>
       <c r="K22" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
@@ -10489,7 +10772,7 @@
       <c r="I23" s="34"/>
       <c r="J23" s="31"/>
       <c r="K23" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
@@ -10548,7 +10831,7 @@
       <c r="I24" s="34"/>
       <c r="J24" s="31"/>
       <c r="K24" s="34" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
@@ -10603,7 +10886,7 @@
       <c r="I25" s="84"/>
       <c r="J25" s="31"/>
       <c r="K25" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
@@ -10622,10 +10905,10 @@
       <c r="X25" s="86"/>
       <c r="Y25" s="87"/>
       <c r="Z25" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA25" s="88" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB25" s="89"/>
       <c r="AC25" s="90" t="s">
@@ -10664,7 +10947,7 @@
       <c r="I26" s="84"/>
       <c r="J26" s="31"/>
       <c r="K26" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
@@ -10723,7 +11006,7 @@
       <c r="I27" s="84"/>
       <c r="J27" s="31"/>
       <c r="K27" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
@@ -10784,7 +11067,7 @@
       <c r="I28" s="84"/>
       <c r="J28" s="31"/>
       <c r="K28" s="84" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
@@ -10862,10 +11145,10 @@
       <c r="AB29" s="102"/>
       <c r="AC29" s="103"/>
       <c r="AD29" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AE29" s="104" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AF29" s="105"/>
       <c r="AG29" s="106" t="s">
@@ -13664,7 +13947,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q160"/>
+  <dimension ref="A1:Q197"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -13783,10 +14066,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>212</v>
@@ -13800,7 +14083,7 @@
         <v>177</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="K6" s="2"/>
     </row>
@@ -13815,7 +14098,7 @@
         <v>261</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -14266,7 +14549,7 @@
         <v>228</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K40" s="2"/>
     </row>
@@ -14275,7 +14558,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -14295,10 +14578,10 @@
         <v>256</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
@@ -14306,10 +14589,10 @@
         <v>257</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
@@ -14317,10 +14600,10 @@
         <v>258</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -14328,10 +14611,10 @@
         <v>260</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -14339,13 +14622,13 @@
         <v>157</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>261</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
@@ -14353,10 +14636,10 @@
         <v>259</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14390,7 +14673,7 @@
         <v>261</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
@@ -14401,7 +14684,7 @@
         <v>266</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
@@ -14412,7 +14695,7 @@
         <v>267</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="52" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14420,7 +14703,7 @@
         <v>171</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -14440,16 +14723,14 @@
         <v>131</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C53" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="D53" s="2">
-        <v>0.5</v>
-      </c>
+      <c r="D53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
@@ -14457,7 +14738,7 @@
         <v>132</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>261</v>
@@ -14466,7 +14747,7 @@
         <v>0.5</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
@@ -14483,7 +14764,7 @@
         <v>0.5</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>270</v>
+        <v>605</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
@@ -14491,13 +14772,13 @@
         <v>158</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>261</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
@@ -14505,13 +14786,13 @@
         <v>166</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>261</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -14519,37 +14800,37 @@
         <v>167</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>261</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C59" s="25"/>
       <c r="K59" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C60" s="25"/>
       <c r="K60" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -14557,13 +14838,13 @@
         <v>162</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
@@ -14571,13 +14852,13 @@
         <v>164</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
@@ -14585,61 +14866,61 @@
         <v>155</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C63" s="25" t="s">
         <v>261</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C64" s="25"/>
       <c r="K64" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C65" s="25"/>
       <c r="K65" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C66" s="25"/>
       <c r="K66" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C67" s="25"/>
       <c r="K67" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
@@ -14647,13 +14928,13 @@
         <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
@@ -14661,13 +14942,13 @@
         <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
@@ -14675,13 +14956,13 @@
         <v>151</v>
       </c>
       <c r="B70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
@@ -14689,13 +14970,13 @@
         <v>153</v>
       </c>
       <c r="B71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -14703,14 +14984,14 @@
         <v>133</v>
       </c>
       <c r="B72" s="151" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C72" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
@@ -14718,29 +14999,29 @@
         <v>135</v>
       </c>
       <c r="B73" s="151" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C73" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="150" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B74" s="151" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C74" s="152" t="s">
         <v>261</v>
       </c>
       <c r="H74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14748,7 +15029,7 @@
         <v>171</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -14768,13 +15049,13 @@
         <v>163</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.35">
@@ -14782,13 +15063,13 @@
         <v>165</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.35">
@@ -14796,14 +15077,14 @@
         <v>168</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C78" s="25" t="s">
         <v>261</v>
       </c>
       <c r="H78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.35">
@@ -14811,13 +15092,13 @@
         <v>156</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.35">
@@ -14825,13 +15106,13 @@
         <v>152</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.35">
@@ -14839,13 +15120,13 @@
         <v>150</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.35">
@@ -14853,13 +15134,13 @@
         <v>154</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.35">
@@ -14867,13 +15148,13 @@
         <v>134</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -14881,7 +15162,7 @@
         <v>171</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -14898,99 +15179,99 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="B85" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="B85" s="23" t="s">
-        <v>351</v>
-      </c>
       <c r="K85" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="B86" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="B86" s="23" t="s">
-        <v>353</v>
-      </c>
       <c r="K86" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B87" t="s">
         <v>354</v>
       </c>
-      <c r="B87" t="s">
+      <c r="H87" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="K87" s="2"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="B89" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="B89" s="23" t="s">
-        <v>359</v>
-      </c>
       <c r="K89" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K90" s="2"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K91" s="2"/>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="K92" s="2"/>
     </row>
@@ -14999,7 +15280,7 @@
         <v>171</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C93" s="17"/>
       <c r="D93" s="17"/>
@@ -15019,10 +15300,10 @@
         <v>252</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
@@ -15030,10 +15311,10 @@
         <v>253</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
@@ -15041,10 +15322,10 @@
         <v>254</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
@@ -15052,150 +15333,150 @@
         <v>255</v>
       </c>
       <c r="B97" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="22" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="B102" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="B102" s="23" t="s">
-        <v>409</v>
-      </c>
       <c r="K102" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="22" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B105" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B106" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B107" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H109" s="21" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="134" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B110" s="135" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
@@ -15203,15 +15484,15 @@
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
       <c r="H110" s="136" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="134" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B111" s="135" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
@@ -15219,15 +15500,15 @@
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
       <c r="H111" s="136" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="134" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B112" s="158" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="7"/>
@@ -15235,15 +15516,15 @@
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
       <c r="H112" s="136" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="134" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B113" s="158" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
@@ -15251,15 +15532,15 @@
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="136" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="134" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B114" s="158" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
@@ -15267,15 +15548,15 @@
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
       <c r="H114" s="136" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B115" s="158" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
@@ -15283,15 +15564,15 @@
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="136" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="134" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B116" s="158" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="7"/>
@@ -15299,15 +15580,15 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="136" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B117" s="158" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
@@ -15315,15 +15596,15 @@
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
       <c r="H117" s="136" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="134" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B118" s="158" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="7"/>
@@ -15331,15 +15612,15 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="136" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B119" s="158" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="7"/>
@@ -15347,15 +15628,15 @@
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
       <c r="H119" s="136" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="134" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B120" s="158" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C120" s="8"/>
       <c r="D120" s="7"/>
@@ -15363,7 +15644,7 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="136" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -15371,7 +15652,7 @@
         <v>125</v>
       </c>
       <c r="B121" s="137" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>196</v>
@@ -15381,19 +15662,19 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="138" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="122" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="139" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B122" s="140" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C122" s="11"/>
       <c r="H122" s="141" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
@@ -15402,14 +15683,14 @@
     </row>
     <row r="123" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="139" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B123" s="140" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C123" s="11"/>
       <c r="H123" s="141" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I123" s="11"/>
       <c r="J123" s="11"/>
@@ -15418,14 +15699,14 @@
     </row>
     <row r="124" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="139" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B124" s="140" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C124" s="11"/>
       <c r="H124" s="141" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
@@ -15434,14 +15715,14 @@
     </row>
     <row r="125" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="139" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B125" s="140" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C125" s="11"/>
       <c r="H125" s="141" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I125" s="11"/>
       <c r="J125" s="11"/>
@@ -15450,14 +15731,14 @@
     </row>
     <row r="126" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="139" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B126" s="140" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C126" s="11"/>
       <c r="H126" s="141" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I126" s="11"/>
       <c r="J126" s="11"/>
@@ -15466,14 +15747,14 @@
     </row>
     <row r="127" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="139" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B127" s="140" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C127" s="11"/>
       <c r="H127" s="141" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I127" s="11"/>
       <c r="J127" s="11"/>
@@ -15482,14 +15763,14 @@
     </row>
     <row r="128" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="139" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B128" s="140" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C128" s="11"/>
       <c r="H128" s="141" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
@@ -15498,14 +15779,14 @@
     </row>
     <row r="129" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="139" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B129" s="140" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C129" s="11"/>
       <c r="H129" s="141" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
@@ -15514,14 +15795,14 @@
     </row>
     <row r="130" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="139" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B130" s="140" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C130" s="11"/>
       <c r="H130" s="141" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
@@ -15530,14 +15811,14 @@
     </row>
     <row r="131" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="139" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B131" s="140" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C131" s="11"/>
       <c r="H131" s="141" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
@@ -15549,13 +15830,13 @@
         <v>126</v>
       </c>
       <c r="B132" s="142" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>196</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I132" s="11"/>
       <c r="J132" s="11"/>
@@ -15564,14 +15845,14 @@
     </row>
     <row r="133" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="143" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B133" s="144" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C133" s="145"/>
       <c r="H133" s="147" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="I133" s="145"/>
       <c r="J133" s="145"/>
@@ -15580,14 +15861,14 @@
     </row>
     <row r="134" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="143" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B134" s="144" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C134" s="145"/>
       <c r="H134" s="147" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="I134" s="145"/>
       <c r="J134" s="145"/>
@@ -15596,14 +15877,14 @@
     </row>
     <row r="135" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="143" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B135" s="144" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C135" s="145"/>
       <c r="H135" s="147" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I135" s="145"/>
       <c r="J135" s="145"/>
@@ -15612,14 +15893,14 @@
     </row>
     <row r="136" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="143" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B136" s="144" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C136" s="145"/>
       <c r="H136" s="147" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I136" s="145"/>
       <c r="J136" s="145"/>
@@ -15628,14 +15909,14 @@
     </row>
     <row r="137" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="143" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B137" s="144" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C137" s="145"/>
       <c r="H137" s="147" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I137" s="145"/>
       <c r="J137" s="145"/>
@@ -15644,14 +15925,14 @@
     </row>
     <row r="138" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="143" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B138" s="144" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C138" s="145"/>
       <c r="H138" s="147" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I138" s="145"/>
       <c r="J138" s="145"/>
@@ -15660,14 +15941,14 @@
     </row>
     <row r="139" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="143" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B139" s="144" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C139" s="145"/>
       <c r="H139" s="147" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I139" s="145"/>
       <c r="J139" s="145"/>
@@ -15676,14 +15957,14 @@
     </row>
     <row r="140" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="143" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B140" s="144" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C140" s="145"/>
       <c r="H140" s="147" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I140" s="145"/>
       <c r="J140" s="145"/>
@@ -15692,14 +15973,14 @@
     </row>
     <row r="141" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="143" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B141" s="144" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C141" s="145"/>
       <c r="H141" s="147" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I141" s="145"/>
       <c r="J141" s="145"/>
@@ -15708,14 +15989,14 @@
     </row>
     <row r="142" spans="1:16" s="146" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="143" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B142" s="144" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C142" s="145"/>
       <c r="H142" s="147" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="I142" s="145"/>
       <c r="J142" s="145"/>
@@ -15727,13 +16008,13 @@
         <v>127</v>
       </c>
       <c r="B143" s="149" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C143" s="145" t="s">
         <v>196</v>
       </c>
       <c r="H143" s="144" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I143" s="145"/>
       <c r="J143" s="145"/>
@@ -15745,13 +16026,13 @@
         <v>124</v>
       </c>
       <c r="B144" s="155" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C144" s="156" t="s">
         <v>196</v>
       </c>
       <c r="H144" s="156" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I144" s="156"/>
       <c r="J144" s="156"/>
@@ -15763,7 +16044,7 @@
         <v>171</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C145" s="17"/>
       <c r="D145" s="17"/>
@@ -15780,206 +16061,645 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="150" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B146" s="151" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B147" t="s">
+        <v>501</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="C148" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A149" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H148" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="15" t="s">
+      <c r="H149" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A150" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B149" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="C149" s="17"/>
-      <c r="D149" s="17"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="17"/>
-      <c r="I149" s="17"/>
-      <c r="J149" s="17"/>
-      <c r="K149" s="17"/>
-      <c r="L149" s="17"/>
-      <c r="N149" s="17"/>
-      <c r="O149" s="17"/>
-      <c r="P149" s="17"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A150" s="150" t="s">
+      <c r="B151" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="C151" s="17"/>
+      <c r="D151" s="17"/>
+      <c r="E151" s="17"/>
+      <c r="F151" s="17"/>
+      <c r="G151" s="17"/>
+      <c r="I151" s="17"/>
+      <c r="J151" s="17"/>
+      <c r="K151" s="17"/>
+      <c r="L151" s="17"/>
+      <c r="N151" s="17"/>
+      <c r="O151" s="17"/>
+      <c r="P151" s="17"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A152" s="150" t="s">
         <v>160</v>
       </c>
-      <c r="B150" s="153" t="s">
+      <c r="B152" s="153" t="s">
+        <v>448</v>
+      </c>
+      <c r="C152" s="152" t="s">
+        <v>261</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="150" t="s">
+        <v>147</v>
+      </c>
+      <c r="B153" s="153" t="s">
         <v>449</v>
       </c>
-      <c r="C150" s="152" t="s">
+      <c r="C153" s="152" t="s">
         <v>261</v>
       </c>
-      <c r="K150" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="150" t="s">
-        <v>147</v>
-      </c>
-      <c r="B151" s="153" t="s">
-        <v>450</v>
-      </c>
-      <c r="C151" s="152" t="s">
-        <v>261</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="150" t="s">
+      <c r="K153" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="150" t="s">
+        <v>520</v>
+      </c>
+      <c r="B154" s="153" t="s">
         <v>521</v>
       </c>
-      <c r="B152" s="153" t="s">
-        <v>522</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A153" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B153" t="s">
-        <v>520</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A154" s="150" t="s">
-        <v>523</v>
-      </c>
-      <c r="B154" s="153" t="s">
-        <v>524</v>
-      </c>
       <c r="K154" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B155" s="159" t="s">
-        <v>525</v>
+        <v>145</v>
+      </c>
+      <c r="B155" t="s">
+        <v>519</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="150" t="s">
-        <v>586</v>
+        <v>522</v>
       </c>
       <c r="B156" s="153" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B157" s="159" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="161" t="s">
-        <v>171</v>
-      </c>
-      <c r="B158" s="162" t="s">
-        <v>542</v>
-      </c>
-      <c r="C158" s="163"/>
-      <c r="D158" s="163"/>
-      <c r="E158" s="163"/>
-      <c r="F158" s="163"/>
-      <c r="G158" s="163"/>
-      <c r="I158" s="163"/>
-      <c r="J158" s="163"/>
-      <c r="K158" s="163"/>
-      <c r="L158" s="163"/>
-      <c r="N158" s="163"/>
-      <c r="O158" s="163"/>
-      <c r="P158" s="163"/>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A158" s="150" t="s">
+        <v>582</v>
+      </c>
+      <c r="B158" s="153" t="s">
+        <v>525</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="B159" t="s">
-        <v>598</v>
+        <v>159</v>
+      </c>
+      <c r="B159" s="159" t="s">
+        <v>526</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="H159" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B160" s="162" t="s">
+        <v>539</v>
+      </c>
+      <c r="C160" s="163"/>
+      <c r="D160" s="163"/>
+      <c r="E160" s="163"/>
+      <c r="F160" s="163"/>
+      <c r="G160" s="163"/>
+      <c r="I160" s="163"/>
+      <c r="J160" s="163"/>
+      <c r="K160" s="163"/>
+      <c r="L160" s="163"/>
+      <c r="N160" s="163"/>
+      <c r="O160" s="163"/>
+      <c r="P160" s="163"/>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A161" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B161" t="s">
         <v>594</v>
       </c>
-      <c r="K159" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A160" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="B160" t="s">
-        <v>593</v>
-      </c>
-      <c r="H160" s="164" t="s">
-        <v>595</v>
+      <c r="H161" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A162" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="B162" t="s">
+        <v>589</v>
+      </c>
+      <c r="H162" s="164" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163" s="162" t="s">
+        <v>647</v>
+      </c>
+      <c r="C163" s="163"/>
+      <c r="D163" s="163"/>
+      <c r="E163" s="163"/>
+      <c r="F163" s="163"/>
+      <c r="G163" s="163"/>
+      <c r="I163" s="163"/>
+      <c r="J163" s="163"/>
+      <c r="K163" s="163"/>
+      <c r="L163" s="163"/>
+      <c r="N163" s="163"/>
+      <c r="O163" s="163"/>
+      <c r="P163" s="163"/>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A164" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B164" t="s">
+        <v>617</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A165" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B165" t="s">
+        <v>616</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A166" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B166" t="s">
+        <v>613</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A167" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B167" t="s">
+        <v>615</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A168" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B168" t="s">
+        <v>626</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A169" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B169" t="s">
+        <v>627</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A170" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B170" t="s">
+        <v>628</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A171" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="B171" t="s">
+        <v>630</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A172" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="B172" t="s">
+        <v>631</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A173" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B173" t="s">
+        <v>633</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A174" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B174" t="s">
+        <v>635</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="K174" s="2"/>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A175" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B175" t="s">
+        <v>632</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A176" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="B176" t="s">
+        <v>640</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A177" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="B177" t="s">
+        <v>642</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A178" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="B178" t="s">
+        <v>645</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A179" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B179" t="s">
+        <v>658</v>
+      </c>
+      <c r="H179" s="2"/>
+      <c r="K179" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A180" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B180" t="s">
+        <v>659</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A181" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B181" t="s">
+        <v>656</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B182" s="162" t="s">
+        <v>648</v>
+      </c>
+      <c r="C182" s="163"/>
+      <c r="D182" s="163"/>
+      <c r="E182" s="163"/>
+      <c r="F182" s="163"/>
+      <c r="G182" s="163"/>
+      <c r="I182" s="163"/>
+      <c r="J182" s="163"/>
+      <c r="K182" s="163"/>
+      <c r="L182" s="163"/>
+      <c r="N182" s="163"/>
+      <c r="O182" s="163"/>
+      <c r="P182" s="163"/>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A183" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B183" t="s">
+        <v>650</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A184" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="B184" t="s">
+        <v>652</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B185" s="162" t="s">
+        <v>654</v>
+      </c>
+      <c r="C185" s="163"/>
+      <c r="D185" s="163"/>
+      <c r="E185" s="163"/>
+      <c r="F185" s="163"/>
+      <c r="G185" s="163"/>
+      <c r="I185" s="163"/>
+      <c r="J185" s="163"/>
+      <c r="K185" s="163"/>
+      <c r="L185" s="163"/>
+      <c r="N185" s="163"/>
+      <c r="O185" s="163"/>
+      <c r="P185" s="163"/>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A186" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="B186" t="s">
+        <v>667</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A187" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="B187" t="s">
+        <v>668</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A188" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B188" t="s">
+        <v>669</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A189" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="B189" t="s">
+        <v>670</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A190" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B190" t="s">
+        <v>671</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A191" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="B191" t="s">
+        <v>672</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A192" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="B192" t="s">
+        <v>680</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A193" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B193" t="s">
+        <v>682</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A194" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B194" t="s">
+        <v>684</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A195" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B195" t="s">
+        <v>685</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A196" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="B196" t="s">
+        <v>683</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A197" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B197" t="s">
+        <v>686</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -15988,14 +16708,14 @@
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K158 K161:K1048576">
+  <conditionalFormatting sqref="K2:K160 K163:K1048576">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(L2&lt;&gt;"",NOT(K2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K159">
+  <conditionalFormatting sqref="K161">
     <cfRule type="expression" dxfId="4" priority="15">
-      <formula>AND(L160&lt;&gt;"",NOT(K159&lt;&gt;""))</formula>
+      <formula>AND(L162&lt;&gt;"",NOT(K161&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -16029,23 +16749,23 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K2:K159 K161:K1048576</xm:sqref>
+          <xm:sqref>K2:K161 K163:K1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0E7D17F-9C98-4BBD-89E8-B63866BAA65B}">
+          <x14:formula1>
+            <xm:f>'Databook Pages'!$A$2:$A$9999</xm:f>
+          </x14:formula1>
+          <xm:sqref>K1:K161 K163:K1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5BACFCF-5A80-4E38-B286-225138198031}">
           <x14:formula1>
             <xm:f>'Population types'!$A$2:$A$9999</xm:f>
           </x14:formula1>
           <xm:sqref>N1:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0E7D17F-9C98-4BBD-89E8-B63866BAA65B}">
-          <x14:formula1>
-            <xm:f>'Databook Pages'!$A$2:$A$9999</xm:f>
-          </x14:formula1>
-          <xm:sqref>K161:K1048576 K1:K159</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16137,13 +16857,13 @@
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>280</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>281</v>
       </c>
       <c r="D3" s="2"/>
       <c r="F3" s="21">
@@ -16152,13 +16872,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B4" t="s">
         <v>282</v>
       </c>
-      <c r="B4" t="s">
-        <v>283</v>
-      </c>
       <c r="C4" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>215</v>
@@ -16167,18 +16887,18 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5" s="21">
         <v>0</v>
@@ -16186,13 +16906,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F6" s="21">
         <v>0</v>
@@ -16200,33 +16920,33 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F7" s="21">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F8" s="21">
         <v>0</v>
@@ -16234,33 +16954,33 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B9" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F10" s="21">
         <v>0</v>
@@ -16268,13 +16988,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>215</v>
@@ -16285,13 +17005,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>215</v>
@@ -16302,13 +17022,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>215</v>
@@ -16319,13 +17039,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B14" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>215</v>
@@ -16336,13 +17056,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>515</v>
+      </c>
+      <c r="B15" t="s">
         <v>516</v>
       </c>
-      <c r="B15" t="s">
-        <v>517</v>
-      </c>
       <c r="C15" s="20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D15" s="2"/>
       <c r="F15" s="21">
@@ -16351,16 +17071,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F16" s="21">
         <v>0</v>
@@ -16368,13 +17088,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>517</v>
+      </c>
+      <c r="B17" t="s">
         <v>518</v>
       </c>
-      <c r="B17" t="s">
-        <v>519</v>
-      </c>
       <c r="C17" s="20" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D17" s="2"/>
       <c r="F17" s="21">
@@ -16383,16 +17103,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B18" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F18" s="21">
         <v>0</v>
@@ -16400,33 +17120,33 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F19" s="21">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F20" s="21">
         <v>0</v>
@@ -16434,13 +17154,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B21" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -16448,13 +17168,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B22" t="s">
+        <v>549</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F22" s="21">
         <v>0</v>
@@ -16462,22 +17182,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B23" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F23" s="21">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -16566,10 +17286,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" t="s">
         <v>383</v>
-      </c>
-      <c r="B2" t="s">
-        <v>384</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -16583,10 +17303,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" t="s">
         <v>385</v>
-      </c>
-      <c r="B3" t="s">
-        <v>386</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -16641,26 +17361,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3139061-44C5-42A6-B9ED-555AB2DC9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4A9E5-9641-43CE-A005-75E9B813D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="8220" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-7720" windowWidth="25820" windowHeight="13900" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="692">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -5474,9 +5474,6 @@
     <t>HBeAg positive HepB (of all)</t>
   </si>
   <si>
-    <t>diag_epos, undiag_epos</t>
-  </si>
-  <si>
     <t>hcc, hcc_d, hcc_l, hcc_t</t>
   </si>
   <si>
@@ -5907,6 +5904,9 @@
   </si>
   <si>
     <t>(qalys_clr+qalys_chb+qalys_cc+qalys_dc+qalys_hcc)*disc_rate_qaly</t>
+  </si>
+  <si>
+    <t>ei,ei_d,ei_l,ei_t,eh,eh_d,eh_l,eh_t</t>
   </si>
 </sst>
 </file>
@@ -7420,18 +7420,18 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>605</v>
+      </c>
+      <c r="B12" t="s">
         <v>606</v>
-      </c>
-      <c r="B12" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -9947,10 +9947,10 @@
       <c r="J8" s="31"/>
       <c r="K8" s="36"/>
       <c r="L8" s="36" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="M8" s="36" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
@@ -10193,9 +10193,7 @@
       <c r="H13" s="40"/>
       <c r="I13" s="40"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="40" t="s">
-        <v>592</v>
-      </c>
+      <c r="K13" s="40"/>
       <c r="L13" s="41"/>
       <c r="M13" s="42"/>
       <c r="N13" s="43" t="s">
@@ -10252,9 +10250,7 @@
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
       <c r="J14" s="31"/>
-      <c r="K14" s="40" t="s">
-        <v>592</v>
-      </c>
+      <c r="K14" s="40"/>
       <c r="L14" s="41"/>
       <c r="M14" s="48"/>
       <c r="N14" s="40"/>
@@ -10309,9 +10305,7 @@
       <c r="H15" s="40"/>
       <c r="I15" s="40"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="40" t="s">
-        <v>592</v>
-      </c>
+      <c r="K15" s="40"/>
       <c r="L15" s="41"/>
       <c r="M15" s="48"/>
       <c r="N15" s="40" t="s">
@@ -10416,7 +10410,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
       <c r="K17" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L17" s="30"/>
       <c r="M17" s="55"/>
@@ -10477,7 +10471,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="31"/>
       <c r="K18" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
@@ -10536,7 +10530,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="31"/>
       <c r="K19" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
@@ -10597,7 +10591,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="31"/>
       <c r="K20" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
@@ -10656,7 +10650,7 @@
       <c r="I21" s="34"/>
       <c r="J21" s="31"/>
       <c r="K21" s="34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
@@ -10715,7 +10709,7 @@
       <c r="I22" s="34"/>
       <c r="J22" s="31"/>
       <c r="K22" s="34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
@@ -10772,7 +10766,7 @@
       <c r="I23" s="34"/>
       <c r="J23" s="31"/>
       <c r="K23" s="34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
@@ -10831,7 +10825,7 @@
       <c r="I24" s="34"/>
       <c r="J24" s="31"/>
       <c r="K24" s="34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
@@ -10886,7 +10880,7 @@
       <c r="I25" s="84"/>
       <c r="J25" s="31"/>
       <c r="K25" s="84" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
@@ -10947,7 +10941,7 @@
       <c r="I26" s="84"/>
       <c r="J26" s="31"/>
       <c r="K26" s="84" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
@@ -11006,7 +11000,7 @@
       <c r="I27" s="84"/>
       <c r="J27" s="31"/>
       <c r="K27" s="84" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
@@ -11067,7 +11061,7 @@
       <c r="I28" s="84"/>
       <c r="J28" s="31"/>
       <c r="K28" s="84" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
@@ -14066,10 +14060,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
+        <v>583</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>584</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>585</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>212</v>
@@ -14083,7 +14077,7 @@
         <v>177</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K6" s="2"/>
     </row>
@@ -14098,7 +14092,7 @@
         <v>261</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -14549,7 +14543,7 @@
         <v>228</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K40" s="2"/>
     </row>
@@ -14764,7 +14758,7 @@
         <v>0.5</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
@@ -14976,7 +14970,7 @@
         <v>261</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -15011,10 +15005,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="150" t="s">
+        <v>591</v>
+      </c>
+      <c r="B74" s="151" t="s">
         <v>592</v>
-      </c>
-      <c r="B74" s="151" t="s">
-        <v>593</v>
       </c>
       <c r="C74" s="152" t="s">
         <v>261</v>
@@ -15374,7 +15368,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="22" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B101" s="23" t="s">
         <v>397</v>
@@ -15424,7 +15418,7 @@
         <v>374</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
@@ -15435,7 +15429,7 @@
         <v>376</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
@@ -15446,7 +15440,7 @@
         <v>375</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
@@ -15457,7 +15451,7 @@
         <v>377</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
@@ -15468,7 +15462,7 @@
         <v>398</v>
       </c>
       <c r="H109" s="21" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
@@ -15644,7 +15638,7 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="136" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -15662,7 +15656,7 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="138" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="122" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35">
@@ -15674,7 +15668,7 @@
       </c>
       <c r="C122" s="11"/>
       <c r="H122" s="141" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
@@ -15770,7 +15764,7 @@
       </c>
       <c r="C128" s="11"/>
       <c r="H128" s="141" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
@@ -15786,7 +15780,7 @@
       </c>
       <c r="C129" s="11"/>
       <c r="H129" s="141" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
@@ -15802,7 +15796,7 @@
       </c>
       <c r="C130" s="11"/>
       <c r="H130" s="141" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
@@ -15818,7 +15812,7 @@
       </c>
       <c r="C131" s="11"/>
       <c r="H131" s="141" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
@@ -15836,7 +15830,7 @@
         <v>196</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I132" s="11"/>
       <c r="J132" s="11"/>
@@ -15852,7 +15846,7 @@
       </c>
       <c r="C133" s="145"/>
       <c r="H133" s="147" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I133" s="145"/>
       <c r="J133" s="145"/>
@@ -15868,7 +15862,7 @@
       </c>
       <c r="C134" s="145"/>
       <c r="H134" s="147" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I134" s="145"/>
       <c r="J134" s="145"/>
@@ -15948,7 +15942,7 @@
       </c>
       <c r="C139" s="145"/>
       <c r="H139" s="147" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I139" s="145"/>
       <c r="J139" s="145"/>
@@ -15964,7 +15958,7 @@
       </c>
       <c r="C140" s="145"/>
       <c r="H140" s="147" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I140" s="145"/>
       <c r="J140" s="145"/>
@@ -15980,7 +15974,7 @@
       </c>
       <c r="C141" s="145"/>
       <c r="H141" s="147" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="I141" s="145"/>
       <c r="J141" s="145"/>
@@ -15996,7 +15990,7 @@
       </c>
       <c r="C142" s="145"/>
       <c r="H142" s="147" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I142" s="145"/>
       <c r="J142" s="145"/>
@@ -16014,7 +16008,7 @@
         <v>196</v>
       </c>
       <c r="H143" s="144" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I143" s="145"/>
       <c r="J143" s="145"/>
@@ -16094,30 +16088,30 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>603</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>261</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="151" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.35">
@@ -16190,7 +16184,7 @@
         <v>261</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
@@ -16215,12 +16209,12 @@
         <v>261</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="150" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B158" s="153" t="s">
         <v>525</v>
@@ -16240,7 +16234,7 @@
         <v>261</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="160" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -16265,13 +16259,13 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B161" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>538</v>
@@ -16279,13 +16273,13 @@
     </row>
     <row r="162" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B162" t="s">
         <v>588</v>
       </c>
-      <c r="B162" t="s">
-        <v>589</v>
-      </c>
       <c r="H162" s="164" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="163" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -16293,7 +16287,7 @@
         <v>171</v>
       </c>
       <c r="B163" s="162" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C163" s="163"/>
       <c r="D163" s="163"/>
@@ -16310,202 +16304,202 @@
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B164" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B165" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B166" t="s">
         <v>612</v>
       </c>
-      <c r="B166" t="s">
+      <c r="H166" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B167" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B168" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B169" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B170" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B171" t="s">
         <v>629</v>
       </c>
-      <c r="B171" t="s">
-        <v>630</v>
-      </c>
       <c r="H171" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B172" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B173" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="B174" t="s">
         <v>634</v>
       </c>
-      <c r="B174" t="s">
+      <c r="H174" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="H174" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="K174" s="2"/>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B175" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B176" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="B177" t="s">
         <v>641</v>
       </c>
-      <c r="B177" t="s">
+      <c r="H177" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="H177" s="2" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B178" t="s">
         <v>644</v>
       </c>
-      <c r="B178" t="s">
+      <c r="H178" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B179" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H179" s="2"/>
       <c r="K179" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B180" t="s">
+        <v>658</v>
+      </c>
+      <c r="H180" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="H180" s="2" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B181" t="s">
         <v>655</v>
       </c>
-      <c r="B181" t="s">
+      <c r="H181" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="H181" s="2" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="182" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -16513,7 +16507,7 @@
         <v>171</v>
       </c>
       <c r="B182" s="162" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C182" s="163"/>
       <c r="D182" s="163"/>
@@ -16530,24 +16524,24 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B183" t="s">
         <v>649</v>
       </c>
-      <c r="B183" t="s">
-        <v>650</v>
-      </c>
       <c r="K183" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B184" t="s">
         <v>651</v>
       </c>
-      <c r="B184" t="s">
+      <c r="H184" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="H184" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="185" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -16555,7 +16549,7 @@
         <v>171</v>
       </c>
       <c r="B185" s="162" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C185" s="163"/>
       <c r="D185" s="163"/>
@@ -16572,134 +16566,134 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B186" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B187" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B188" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B189" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B190" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B191" t="s">
+        <v>671</v>
+      </c>
+      <c r="K191" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B192" t="s">
+        <v>679</v>
+      </c>
+      <c r="H192" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B193" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B194" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B195" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B196" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B197" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -16920,10 +16914,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B7" t="s">
         <v>555</v>
-      </c>
-      <c r="B7" t="s">
-        <v>556</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>284</v>
@@ -16954,10 +16948,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" t="s">
         <v>557</v>
-      </c>
-      <c r="B9" t="s">
-        <v>558</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>285</v>
@@ -17042,7 +17036,7 @@
         <v>396</v>
       </c>
       <c r="B14" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>391</v>
@@ -17146,7 +17140,7 @@
         <v>547</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F20" s="21">
         <v>0</v>
@@ -17160,7 +17154,7 @@
         <v>548</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -17174,7 +17168,7 @@
         <v>549</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F22" s="21">
         <v>0</v>
@@ -17188,7 +17182,7 @@
         <v>550</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>551</v>
+        <v>691</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>278</v>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4A9E5-9641-43CE-A005-75E9B813D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56667E5-9367-4EE0-A13D-85268B924DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-7720" windowWidth="25820" windowHeight="13900" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-7720" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="693">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -5907,6 +5907,9 @@
   </si>
   <si>
     <t>ei,ei_d,ei_l,ei_t,eh,eh_d,eh_l,eh_t</t>
+  </si>
+  <si>
+    <t>rate</t>
   </si>
 </sst>
 </file>
@@ -6862,7 +6865,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -6923,6 +6926,48 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -16181,7 +16226,7 @@
         <v>519</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>261</v>
+        <v>692</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>580</v>
@@ -16206,7 +16251,7 @@
         <v>524</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>261</v>
+        <v>692</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>595</v>
@@ -16231,7 +16276,7 @@
         <v>526</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>261</v>
+        <v>692</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>596</v>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56667E5-9367-4EE0-A13D-85268B924DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EB52E5-EB6B-4CB5-A56D-5F5557195381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-7720" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="737">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -5774,24 +5774,6 @@
     <t>Direct Costs of Hepatitis B</t>
   </si>
   <si>
-    <t>Placeholder mortality costs</t>
-  </si>
-  <si>
-    <t>stat_year_life</t>
-  </si>
-  <si>
-    <t>Value for a lost statistical year of life in Australia</t>
-  </si>
-  <si>
-    <t>mort_cost</t>
-  </si>
-  <si>
-    <t>Cost of HBV attributable deaths in Australia</t>
-  </si>
-  <si>
-    <t>hep_dth*stat_year_life*disc_rate_cost</t>
-  </si>
-  <si>
     <t>QALYs</t>
   </si>
   <si>
@@ -5910,6 +5892,156 @@
   </si>
   <si>
     <t>rate</t>
+  </si>
+  <si>
+    <t>Productivity loss from mortality (15-64y)</t>
+  </si>
+  <si>
+    <t>annual_salary</t>
+  </si>
+  <si>
+    <t>Estimated annual salary of full -time Australian employee (median)</t>
+  </si>
+  <si>
+    <t>etp_ratio</t>
+  </si>
+  <si>
+    <t>Employment to population ratio in Australia</t>
+  </si>
+  <si>
+    <t>sh_prod</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>prod_loss</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (15-19)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (20-24)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (25-29)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (30-34)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (35-39)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (40-44)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (45-49)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (50-54)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (55-59)</t>
+  </si>
+  <si>
+    <t>Years Productive Life Lost (60-64)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (15-19)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (20-24)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (25-29)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (30-34)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (35-39)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (40-44)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (45-49)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (50-54)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (55-59)</t>
+  </si>
+  <si>
+    <t>Proportion of HBV deaths (60-64)</t>
+  </si>
+  <si>
+    <t>Productivity loss caused by hepatitis B attributable mortality</t>
+  </si>
+  <si>
+    <t>ypll_1519</t>
+  </si>
+  <si>
+    <t>dp_1519</t>
+  </si>
+  <si>
+    <t>ypll_2024</t>
+  </si>
+  <si>
+    <t>dp_2024</t>
+  </si>
+  <si>
+    <t>ypll_2529</t>
+  </si>
+  <si>
+    <t>dp_2529</t>
+  </si>
+  <si>
+    <t>ypll_3034</t>
+  </si>
+  <si>
+    <t>dp_3034</t>
+  </si>
+  <si>
+    <t>ypll_3539</t>
+  </si>
+  <si>
+    <t>dp_3539</t>
+  </si>
+  <si>
+    <t>ypll_4044</t>
+  </si>
+  <si>
+    <t>dp_4044</t>
+  </si>
+  <si>
+    <t>ypll_4549</t>
+  </si>
+  <si>
+    <t>dp_4549</t>
+  </si>
+  <si>
+    <t>ypll_5054</t>
+  </si>
+  <si>
+    <t>dp_5054</t>
+  </si>
+  <si>
+    <t>ypll_5559</t>
+  </si>
+  <si>
+    <t>dp_5559</t>
+  </si>
+  <si>
+    <t>ypll_6064</t>
+  </si>
+  <si>
+    <t>dp_6064</t>
+  </si>
+  <si>
+    <t>disc_rate_cost*annual_salary*etp_ratio*((ypll_1519*dp_1519*hep_dth)+(ypll_2024*dp_2024*hep_dth)+(ypll_2529*dp_2529*hep_dth)+(ypll_3034*dp_3034*hep_dth)+(ypll_3539*dp_3539*hep_dth)+(ypll_4044*dp_4044*hep_dth)+(ypll_4549*dp_4549*hep_dth)+(ypll_5054*dp_5054*hep_dth)+(ypll_5559*dp_5559*hep_dth)+(ypll_6064*dp_6064*hep_dth))</t>
   </si>
 </sst>
 </file>
@@ -6865,7 +6997,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill>
@@ -6926,48 +7058,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7368,7 +7458,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" customWidth="1"/>
@@ -7473,10 +7563,18 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="B13" t="s">
-        <v>653</v>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>692</v>
+      </c>
+      <c r="B14" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -13986,7 +14084,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q197"/>
+  <dimension ref="A1:Q218"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -16226,7 +16324,7 @@
         <v>519</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>580</v>
@@ -16251,7 +16349,7 @@
         <v>524</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>595</v>
@@ -16276,7 +16374,7 @@
         <v>526</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>596</v>
@@ -16518,7 +16616,7 @@
         <v>610</v>
       </c>
       <c r="B179" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="H179" s="2"/>
       <c r="K179" s="2" t="s">
@@ -16530,21 +16628,21 @@
         <v>607</v>
       </c>
       <c r="B180" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B181" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="182" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
@@ -16552,7 +16650,7 @@
         <v>171</v>
       </c>
       <c r="B182" s="162" t="s">
-        <v>647</v>
+        <v>687</v>
       </c>
       <c r="C182" s="163"/>
       <c r="D182" s="163"/>
@@ -16569,176 +16667,428 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="B183" t="s">
-        <v>649</v>
+        <v>689</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>605</v>
+        <v>692</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>650</v>
+        <v>690</v>
       </c>
       <c r="B184" t="s">
-        <v>651</v>
-      </c>
-      <c r="H184" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="161" t="s">
-        <v>171</v>
-      </c>
-      <c r="B185" s="162" t="s">
-        <v>653</v>
-      </c>
-      <c r="C185" s="163"/>
-      <c r="D185" s="163"/>
-      <c r="E185" s="163"/>
-      <c r="F185" s="163"/>
-      <c r="G185" s="163"/>
-      <c r="I185" s="163"/>
-      <c r="J185" s="163"/>
-      <c r="K185" s="163"/>
-      <c r="L185" s="163"/>
-      <c r="N185" s="163"/>
-      <c r="O185" s="163"/>
-      <c r="P185" s="163"/>
+        <v>691</v>
+      </c>
+      <c r="H184" s="2"/>
+      <c r="K184" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A185" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="B185" t="s">
+        <v>695</v>
+      </c>
+      <c r="H185" s="2"/>
+      <c r="K185" s="2" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>660</v>
+        <v>717</v>
       </c>
       <c r="B186" t="s">
-        <v>666</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="H186" s="2"/>
       <c r="K186" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>661</v>
+        <v>718</v>
       </c>
       <c r="B187" t="s">
-        <v>667</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="H187" s="2"/>
       <c r="K187" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>662</v>
+        <v>719</v>
       </c>
       <c r="B188" t="s">
-        <v>668</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="H188" s="2"/>
       <c r="K188" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>663</v>
+        <v>720</v>
       </c>
       <c r="B189" t="s">
-        <v>669</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="H189" s="2"/>
       <c r="K189" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>664</v>
+        <v>721</v>
       </c>
       <c r="B190" t="s">
-        <v>670</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="H190" s="2"/>
       <c r="K190" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>665</v>
+        <v>722</v>
       </c>
       <c r="B191" t="s">
-        <v>671</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="H191" s="2"/>
       <c r="K191" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="B192" t="s">
+        <v>708</v>
+      </c>
+      <c r="H192" s="2"/>
+      <c r="K192" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A193" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B193" t="s">
+        <v>699</v>
+      </c>
+      <c r="H193" s="2"/>
+      <c r="K193" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A194" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="B194" t="s">
+        <v>709</v>
+      </c>
+      <c r="H194" s="2"/>
+      <c r="K194" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A195" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="B195" t="s">
+        <v>700</v>
+      </c>
+      <c r="H195" s="2"/>
+      <c r="K195" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A196" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="B196" t="s">
+        <v>710</v>
+      </c>
+      <c r="H196" s="2"/>
+      <c r="K196" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A197" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="B197" t="s">
+        <v>701</v>
+      </c>
+      <c r="H197" s="2"/>
+      <c r="K197" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A198" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="B198" t="s">
+        <v>711</v>
+      </c>
+      <c r="H198" s="2"/>
+      <c r="K198" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A199" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B199" t="s">
+        <v>702</v>
+      </c>
+      <c r="H199" s="2"/>
+      <c r="K199" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A200" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="B200" t="s">
+        <v>712</v>
+      </c>
+      <c r="H200" s="2"/>
+      <c r="K200" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A201" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="B201" t="s">
+        <v>703</v>
+      </c>
+      <c r="H201" s="2"/>
+      <c r="K201" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A202" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="B202" t="s">
+        <v>713</v>
+      </c>
+      <c r="H202" s="2"/>
+      <c r="K202" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A203" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="B203" t="s">
+        <v>704</v>
+      </c>
+      <c r="H203" s="2"/>
+      <c r="K203" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A204" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="B204" t="s">
+        <v>714</v>
+      </c>
+      <c r="H204" s="2"/>
+      <c r="K204" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A205" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="B205" t="s">
+        <v>715</v>
+      </c>
+      <c r="H205" s="164" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B206" s="162" t="s">
+        <v>647</v>
+      </c>
+      <c r="C206" s="163"/>
+      <c r="D206" s="163"/>
+      <c r="E206" s="163"/>
+      <c r="F206" s="163"/>
+      <c r="G206" s="163"/>
+      <c r="I206" s="163"/>
+      <c r="J206" s="163"/>
+      <c r="K206" s="163"/>
+      <c r="L206" s="163"/>
+      <c r="N206" s="163"/>
+      <c r="O206" s="163"/>
+      <c r="P206" s="163"/>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A207" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B207" t="s">
+        <v>660</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A208" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B208" t="s">
+        <v>661</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A209" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="B209" t="s">
+        <v>662</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A210" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="B210" t="s">
+        <v>663</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A211" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B211" t="s">
+        <v>664</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A212" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="B212" t="s">
+        <v>665</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A213" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B213" t="s">
         <v>673</v>
       </c>
-      <c r="B192" t="s">
+      <c r="H213" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A214" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="B214" t="s">
+        <v>675</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A215" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B215" t="s">
+        <v>677</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A216" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B216" t="s">
+        <v>678</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A217" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B217" t="s">
+        <v>676</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A218" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="B218" t="s">
         <v>679</v>
       </c>
-      <c r="H192" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A193" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="B193" t="s">
-        <v>681</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A194" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="B194" t="s">
-        <v>683</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A195" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="H218" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A196" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="B196" t="s">
-        <v>682</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A197" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="B197" t="s">
-        <v>685</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -17227,7 +17577,7 @@
         <v>550</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>278</v>

--- a/framework/hbv_fw_v2.1_autosave.xlsx
+++ b/framework/hbv_fw_v2.1_autosave.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EB52E5-EB6B-4CB5-A56D-5F5557195381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979F2E16-B7E2-40BD-82C8-AFD3F3364835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="743">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -6042,6 +6042,24 @@
   </si>
   <si>
     <t>disc_rate_cost*annual_salary*etp_ratio*((ypll_1519*dp_1519*hep_dth)+(ypll_2024*dp_2024*hep_dth)+(ypll_2529*dp_2529*hep_dth)+(ypll_3034*dp_3034*hep_dth)+(ypll_3539*dp_3539*hep_dth)+(ypll_4044*dp_4044*hep_dth)+(ypll_4549*dp_4549*hep_dth)+(ypll_5054*dp_5054*hep_dth)+(ypll_5559*dp_5559*hep_dth)+(ypll_6064*dp_6064*hep_dth))</t>
+  </si>
+  <si>
+    <t>dc_death</t>
+  </si>
+  <si>
+    <t>hcc_death</t>
+  </si>
+  <si>
+    <t>Deaths due to decompensated cirrhosis</t>
+  </si>
+  <si>
+    <t>Deaths due to hepatocellular carcinoma</t>
+  </si>
+  <si>
+    <t>dc:snk_hdth+dc_d:snk_hdth+dc_l:snk_hdth+dc_t:snk_hdth</t>
+  </si>
+  <si>
+    <t>hcc:snk_hdth+hcc_d:snk_hdth+hcc_l:snk_hdth+hcc_t:snk_hdth</t>
   </si>
 </sst>
 </file>
@@ -10925,9 +10943,7 @@
         <v>147</v>
       </c>
       <c r="W23" s="34"/>
-      <c r="X23" s="77" t="s">
-        <v>159</v>
-      </c>
+      <c r="X23" s="77"/>
       <c r="Y23" s="74"/>
       <c r="Z23" s="34"/>
       <c r="AA23" s="34" t="s">
@@ -14084,7 +14100,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q218"/>
+  <dimension ref="A1:Q220"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" style="4" bestFit="1" customWidth="1"/>
@@ -16414,109 +16430,115 @@
         <v>538</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B162" t="s">
+        <v>739</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A163" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="B163" t="s">
+        <v>740</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A164" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B164" t="s">
         <v>588</v>
       </c>
-      <c r="H162" s="164" t="s">
+      <c r="H164" s="164" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="163" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="161" t="s">
+    <row r="165" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="161" t="s">
         <v>171</v>
       </c>
-      <c r="B163" s="162" t="s">
+      <c r="B165" s="162" t="s">
         <v>646</v>
       </c>
-      <c r="C163" s="163"/>
-      <c r="D163" s="163"/>
-      <c r="E163" s="163"/>
-      <c r="F163" s="163"/>
-      <c r="G163" s="163"/>
-      <c r="I163" s="163"/>
-      <c r="J163" s="163"/>
-      <c r="K163" s="163"/>
-      <c r="L163" s="163"/>
-      <c r="N163" s="163"/>
-      <c r="O163" s="163"/>
-      <c r="P163" s="163"/>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A164" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="B164" t="s">
-        <v>616</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A165" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="B165" t="s">
-        <v>615</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>605</v>
-      </c>
+      <c r="C165" s="163"/>
+      <c r="D165" s="163"/>
+      <c r="E165" s="163"/>
+      <c r="F165" s="163"/>
+      <c r="G165" s="163"/>
+      <c r="I165" s="163"/>
+      <c r="J165" s="163"/>
+      <c r="K165" s="163"/>
+      <c r="L165" s="163"/>
+      <c r="N165" s="163"/>
+      <c r="O165" s="163"/>
+      <c r="P165" s="163"/>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B166" t="s">
-        <v>612</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B167" t="s">
-        <v>614</v>
-      </c>
-      <c r="H167" s="2" t="s">
-        <v>638</v>
+        <v>615</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B168" t="s">
-        <v>625</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>605</v>
+        <v>612</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="B169" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B170" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="K170" s="2" t="s">
         <v>605</v>
@@ -16524,21 +16546,21 @@
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B171" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B172" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K172" s="2" t="s">
         <v>605</v>
@@ -16546,33 +16568,32 @@
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B173" t="s">
-        <v>632</v>
-      </c>
-      <c r="K173" s="2" t="s">
-        <v>605</v>
+        <v>629</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="B174" t="s">
-        <v>634</v>
-      </c>
-      <c r="H174" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="K174" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B175" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>605</v>
@@ -16580,132 +16601,131 @@
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="B176" t="s">
-        <v>639</v>
-      </c>
-      <c r="K176" s="2" t="s">
-        <v>605</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="K176" s="2"/>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="B177" t="s">
-        <v>641</v>
-      </c>
-      <c r="H177" s="2" t="s">
-        <v>642</v>
+        <v>631</v>
+      </c>
+      <c r="K177" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>643</v>
+        <v>623</v>
       </c>
       <c r="B178" t="s">
-        <v>644</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="B179" t="s">
-        <v>651</v>
-      </c>
-      <c r="H179" s="2"/>
-      <c r="K179" s="2" t="s">
-        <v>605</v>
+        <v>641</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>607</v>
+        <v>643</v>
       </c>
       <c r="B180" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>648</v>
+        <v>610</v>
       </c>
       <c r="B181" t="s">
-        <v>649</v>
-      </c>
-      <c r="H181" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="161" t="s">
-        <v>171</v>
-      </c>
-      <c r="B182" s="162" t="s">
-        <v>687</v>
-      </c>
-      <c r="C182" s="163"/>
-      <c r="D182" s="163"/>
-      <c r="E182" s="163"/>
-      <c r="F182" s="163"/>
-      <c r="G182" s="163"/>
-      <c r="I182" s="163"/>
-      <c r="J182" s="163"/>
-      <c r="K182" s="163"/>
-      <c r="L182" s="163"/>
-      <c r="N182" s="163"/>
-      <c r="O182" s="163"/>
-      <c r="P182" s="163"/>
+        <v>651</v>
+      </c>
+      <c r="H181" s="2"/>
+      <c r="K181" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A182" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B182" t="s">
+        <v>652</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
       <c r="B183" t="s">
-        <v>689</v>
-      </c>
-      <c r="K183" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A184" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="B184" t="s">
-        <v>691</v>
-      </c>
-      <c r="H184" s="2"/>
-      <c r="K184" s="2" t="s">
-        <v>692</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B184" s="162" t="s">
+        <v>687</v>
+      </c>
+      <c r="C184" s="163"/>
+      <c r="D184" s="163"/>
+      <c r="E184" s="163"/>
+      <c r="F184" s="163"/>
+      <c r="G184" s="163"/>
+      <c r="I184" s="163"/>
+      <c r="J184" s="163"/>
+      <c r="K184" s="163"/>
+      <c r="L184" s="163"/>
+      <c r="N184" s="163"/>
+      <c r="O184" s="163"/>
+      <c r="P184" s="163"/>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="B185" t="s">
-        <v>695</v>
-      </c>
-      <c r="H185" s="2"/>
+        <v>689</v>
+      </c>
       <c r="K185" s="2" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="B186" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="H186" s="2"/>
       <c r="K186" s="2" t="s">
@@ -16714,10 +16734,10 @@
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B187" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H187" s="2"/>
       <c r="K187" s="2" t="s">
@@ -16726,10 +16746,10 @@
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B188" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H188" s="2"/>
       <c r="K188" s="2" t="s">
@@ -16738,10 +16758,10 @@
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B189" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H189" s="2"/>
       <c r="K189" s="2" t="s">
@@ -16750,10 +16770,10 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B190" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H190" s="2"/>
       <c r="K190" s="2" t="s">
@@ -16762,10 +16782,10 @@
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B191" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H191" s="2"/>
       <c r="K191" s="2" t="s">
@@ -16774,10 +16794,10 @@
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B192" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H192" s="2"/>
       <c r="K192" s="2" t="s">
@@ -16786,10 +16806,10 @@
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B193" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H193" s="2"/>
       <c r="K193" s="2" t="s">
@@ -16798,10 +16818,10 @@
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B194" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H194" s="2"/>
       <c r="K194" s="2" t="s">
@@ -16810,10 +16830,10 @@
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B195" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H195" s="2"/>
       <c r="K195" s="2" t="s">
@@ -16822,10 +16842,10 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B196" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H196" s="2"/>
       <c r="K196" s="2" t="s">
@@ -16834,10 +16854,10 @@
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B197" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H197" s="2"/>
       <c r="K197" s="2" t="s">
@@ -16846,10 +16866,10 @@
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B198" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H198" s="2"/>
       <c r="K198" s="2" t="s">
@@ -16858,10 +16878,10 @@
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B199" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H199" s="2"/>
       <c r="K199" s="2" t="s">
@@ -16870,10 +16890,10 @@
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B200" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H200" s="2"/>
       <c r="K200" s="2" t="s">
@@ -16882,10 +16902,10 @@
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B201" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H201" s="2"/>
       <c r="K201" s="2" t="s">
@@ -16894,10 +16914,10 @@
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B202" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H202" s="2"/>
       <c r="K202" s="2" t="s">
@@ -16906,10 +16926,10 @@
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B203" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H203" s="2"/>
       <c r="K203" s="2" t="s">
@@ -16918,75 +16938,77 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H204" s="2"/>
       <c r="K204" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="B205" t="s">
+        <v>704</v>
+      </c>
+      <c r="H205" s="2"/>
+      <c r="K205" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A206" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="B206" t="s">
+        <v>714</v>
+      </c>
+      <c r="H206" s="2"/>
+      <c r="K206" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A207" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B207" t="s">
         <v>715</v>
       </c>
-      <c r="H205" s="164" t="s">
+      <c r="H207" s="164" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="206" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="161" t="s">
+    <row r="208" spans="1:16" s="162" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="161" t="s">
         <v>171</v>
       </c>
-      <c r="B206" s="162" t="s">
+      <c r="B208" s="162" t="s">
         <v>647</v>
       </c>
-      <c r="C206" s="163"/>
-      <c r="D206" s="163"/>
-      <c r="E206" s="163"/>
-      <c r="F206" s="163"/>
-      <c r="G206" s="163"/>
-      <c r="I206" s="163"/>
-      <c r="J206" s="163"/>
-      <c r="K206" s="163"/>
-      <c r="L206" s="163"/>
-      <c r="N206" s="163"/>
-      <c r="O206" s="163"/>
-      <c r="P206" s="163"/>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A207" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="B207" t="s">
-        <v>660</v>
-      </c>
-      <c r="K207" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A208" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="B208" t="s">
-        <v>661</v>
-      </c>
-      <c r="K208" s="2" t="s">
-        <v>666</v>
-      </c>
+      <c r="C208" s="163"/>
+      <c r="D208" s="163"/>
+      <c r="E208" s="163"/>
+      <c r="F208" s="163"/>
+      <c r="G208" s="163"/>
+      <c r="I208" s="163"/>
+      <c r="J208" s="163"/>
+      <c r="K208" s="163"/>
+      <c r="L208" s="163"/>
+      <c r="N208" s="163"/>
+      <c r="O208" s="163"/>
+      <c r="P208" s="163"/>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B209" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K209" s="2" t="s">
         <v>666</v>
@@ -16994,10 +17016,10 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B210" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K210" s="2" t="s">
         <v>666</v>
@@ -17005,10 +17027,10 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B211" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>666</v>
@@ -17016,10 +17038,10 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B212" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K212" s="2" t="s">
         <v>666</v>
@@ -17027,67 +17049,89 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="B213" t="s">
-        <v>673</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="B214" t="s">
-        <v>675</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>680</v>
+        <v>665</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B215" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B216" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B217" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B218" t="s">
+        <v>678</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A219" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B219" t="s">
+        <v>676</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A220" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B220" t="s">
         <v>679</v>
       </c>
-      <c r="H218" s="2" t="s">
+      <c r="H220" s="2" t="s">
         <v>684</v>
       </c>
     </row>
@@ -17097,14 +17141,14 @@
       <formula>AND(A1&lt;&gt;"",NOT(B1&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K160 K163:K1048576">
+  <conditionalFormatting sqref="K2:K160 K165:K1048576">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(L2&lt;&gt;"",NOT(K2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K161">
+  <conditionalFormatting sqref="K161:K163">
     <cfRule type="expression" dxfId="4" priority="15">
-      <formula>AND(L162&lt;&gt;"",NOT(K161&lt;&gt;""))</formula>
+      <formula>AND(L164&lt;&gt;"",NOT(K161&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -17138,7 +17182,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K2:K161 K163:K1048576</xm:sqref>
+          <xm:sqref>K2:K163 K165:K1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -17148,7 +17192,7 @@
           <x14:formula1>
             <xm:f>'Databook Pages'!$A$2:$A$9999</xm:f>
           </x14:formula1>
-          <xm:sqref>K1:K161 K163:K1048576</xm:sqref>
+          <xm:sqref>K1:K163 K165:K1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5BACFCF-5A80-4E38-B286-225138198031}">
           <x14:formula1>
